--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13035,7 +13035,7 @@
         <v>46084</v>
       </c>
       <c r="B428" t="n">
-        <v>30.12</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="429">
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13043,7 +13043,7 @@
         <v>46085</v>
       </c>
       <c r="B429" t="n">
-        <v>30.12</v>
+        <v>54.18</v>
       </c>
     </row>
     <row r="430">
@@ -13051,7 +13051,7 @@
         <v>46086</v>
       </c>
       <c r="B430" t="n">
-        <v>30.12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="431">
@@ -13059,7 +13059,7 @@
         <v>46087</v>
       </c>
       <c r="B431" t="n">
-        <v>30.12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="432">
@@ -13067,7 +13067,7 @@
         <v>46088</v>
       </c>
       <c r="B432" t="n">
-        <v>30.12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="433">
@@ -13075,7 +13075,7 @@
         <v>46089</v>
       </c>
       <c r="B433" t="n">
-        <v>30.12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="434">
@@ -13083,7 +13083,7 @@
         <v>46090</v>
       </c>
       <c r="B434" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="435">
@@ -13091,7 +13091,7 @@
         <v>46091</v>
       </c>
       <c r="B435" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="436">
@@ -13099,7 +13099,7 @@
         <v>46092</v>
       </c>
       <c r="B436" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="437">
@@ -13107,7 +13107,7 @@
         <v>46093</v>
       </c>
       <c r="B437" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="438">
@@ -13115,7 +13115,7 @@
         <v>46094</v>
       </c>
       <c r="B438" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="439">
@@ -13123,7 +13123,7 @@
         <v>46095</v>
       </c>
       <c r="B439" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="440">
@@ -13131,7 +13131,7 @@
         <v>46096</v>
       </c>
       <c r="B440" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="441">
@@ -13139,7 +13139,7 @@
         <v>46097</v>
       </c>
       <c r="B441" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="442">
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>30.77</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>30.5</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>29.79</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>29.76</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>30.21</v>
+        <v>39.51</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>30.21</v>
+        <v>38.32</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>30.31</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>31</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>30.85</v>
+        <v>34.48</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>25.01</v>
+        <v>26.58</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>26.44</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>22.61</v>
+        <v>22.77</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13051,7 +13051,7 @@
         <v>46086</v>
       </c>
       <c r="B430" t="n">
-        <v>42</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="431">
@@ -13059,7 +13059,7 @@
         <v>46087</v>
       </c>
       <c r="B431" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="432">
@@ -13067,7 +13067,7 @@
         <v>46088</v>
       </c>
       <c r="B432" t="n">
-        <v>42</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="433">
@@ -13075,7 +13075,7 @@
         <v>46089</v>
       </c>
       <c r="B433" t="n">
-        <v>42</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="434">
@@ -13083,7 +13083,7 @@
         <v>46090</v>
       </c>
       <c r="B434" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="435">
@@ -13091,7 +13091,7 @@
         <v>46091</v>
       </c>
       <c r="B435" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="436">
@@ -13099,7 +13099,7 @@
         <v>46092</v>
       </c>
       <c r="B436" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="437">
@@ -13107,7 +13107,7 @@
         <v>46093</v>
       </c>
       <c r="B437" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="438">
@@ -13115,7 +13115,7 @@
         <v>46094</v>
       </c>
       <c r="B438" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="439">
@@ -13123,7 +13123,7 @@
         <v>46095</v>
       </c>
       <c r="B439" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="440">
@@ -13131,7 +13131,7 @@
         <v>46096</v>
       </c>
       <c r="B440" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="441">
@@ -13139,7 +13139,7 @@
         <v>46097</v>
       </c>
       <c r="B441" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="442">
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>37.03</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>43.95</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>41.53</v>
+        <v>46.98</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>39.93</v>
+        <v>45.03</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>39.51</v>
+        <v>43.74</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>38.32</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>37.85</v>
+        <v>41.47</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>36.57</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>34.48</v>
+        <v>36.39</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>26.58</v>
+        <v>28.41</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>28.39</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>22.77</v>
+        <v>23.19</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13059,7 +13059,7 @@
         <v>46087</v>
       </c>
       <c r="B431" t="n">
-        <v>47</v>
+        <v>50.58</v>
       </c>
     </row>
     <row r="432">
@@ -13067,7 +13067,7 @@
         <v>46088</v>
       </c>
       <c r="B432" t="n">
-        <v>49.05</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="433">
@@ -13075,7 +13075,7 @@
         <v>46089</v>
       </c>
       <c r="B433" t="n">
-        <v>49.05</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="434">
@@ -13083,7 +13083,7 @@
         <v>46090</v>
       </c>
       <c r="B434" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="435">
@@ -13091,7 +13091,7 @@
         <v>46091</v>
       </c>
       <c r="B435" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="436">
@@ -13099,7 +13099,7 @@
         <v>46092</v>
       </c>
       <c r="B436" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="437">
@@ -13107,7 +13107,7 @@
         <v>46093</v>
       </c>
       <c r="B437" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="438">
@@ -13115,7 +13115,7 @@
         <v>46094</v>
       </c>
       <c r="B438" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="439">
@@ -13123,7 +13123,7 @@
         <v>46095</v>
       </c>
       <c r="B439" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="440">
@@ -13131,7 +13131,7 @@
         <v>46096</v>
       </c>
       <c r="B440" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="441">
@@ -13139,7 +13139,7 @@
         <v>46097</v>
       </c>
       <c r="B441" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="442">
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>50.96</v>
+        <v>49.91</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>47.48</v>
+        <v>49.73</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>46.98</v>
+        <v>49.51</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>45.03</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>43.74</v>
+        <v>45.44</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>42.28</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>41.47</v>
+        <v>43.32</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>39.78</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>36.39</v>
+        <v>38.67</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>28.41</v>
+        <v>29.82</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>30.07</v>
+        <v>31.59</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>23.19</v>
+        <v>23.73</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13067,7 +13067,7 @@
         <v>46088</v>
       </c>
       <c r="B432" t="n">
-        <v>50.75</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="433">
@@ -13075,7 +13075,7 @@
         <v>46089</v>
       </c>
       <c r="B433" t="n">
-        <v>50.75</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="434">
@@ -13083,7 +13083,7 @@
         <v>46090</v>
       </c>
       <c r="B434" t="n">
-        <v>49.91</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="435">
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13091,7 +13091,7 @@
         <v>46091</v>
       </c>
       <c r="B435" t="n">
-        <v>49.91</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="436">
@@ -13099,7 +13099,7 @@
         <v>46092</v>
       </c>
       <c r="B436" t="n">
-        <v>49.91</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="437">
@@ -13107,7 +13107,7 @@
         <v>46093</v>
       </c>
       <c r="B437" t="n">
-        <v>49.91</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="438">
@@ -13115,7 +13115,7 @@
         <v>46094</v>
       </c>
       <c r="B438" t="n">
-        <v>49.91</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="439">
@@ -13123,7 +13123,7 @@
         <v>46095</v>
       </c>
       <c r="B439" t="n">
-        <v>49.91</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="440">
@@ -13131,7 +13131,7 @@
         <v>46096</v>
       </c>
       <c r="B440" t="n">
-        <v>49.91</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="441">
@@ -13139,7 +13139,7 @@
         <v>46097</v>
       </c>
       <c r="B441" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="442">
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>49.91</v>
+        <v>49.09</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>49.73</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>49.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>47.76</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>45.44</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>43.99</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>43.32</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>42.26</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>38.67</v>
+        <v>44.29</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>29.82</v>
+        <v>32.68</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>31.59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>23.73</v>
+        <v>24.84</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13091,7 +13091,7 @@
         <v>46091</v>
       </c>
       <c r="B435" t="n">
-        <v>51.65</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="436">
@@ -13099,7 +13099,7 @@
         <v>46092</v>
       </c>
       <c r="B436" t="n">
-        <v>51.65</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="437">
@@ -13107,7 +13107,7 @@
         <v>46093</v>
       </c>
       <c r="B437" t="n">
-        <v>51.65</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="438">
@@ -13115,7 +13115,7 @@
         <v>46094</v>
       </c>
       <c r="B438" t="n">
-        <v>51.65</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="439">
@@ -13123,7 +13123,7 @@
         <v>46095</v>
       </c>
       <c r="B439" t="n">
-        <v>51.65</v>
+        <v>58.64</v>
       </c>
     </row>
     <row r="440">
@@ -13131,7 +13131,7 @@
         <v>46096</v>
       </c>
       <c r="B440" t="n">
-        <v>51.65</v>
+        <v>58.64</v>
       </c>
     </row>
     <row r="441">
@@ -13139,7 +13139,7 @@
         <v>46097</v>
       </c>
       <c r="B441" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="442">
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>49.09</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>49.09</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>49.09</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>52.65</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>52.65</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>52.65</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>52.65</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>51</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>52.75</v>
+        <v>54.91</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>48.25</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>47.3</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>46.95</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>46.83</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>44.29</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>32.68</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>35</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>24.84</v>
+        <v>26.09</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13099,7 +13099,7 @@
         <v>46092</v>
       </c>
       <c r="B436" t="n">
-        <v>56.04</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="437">
@@ -13107,7 +13107,7 @@
         <v>46093</v>
       </c>
       <c r="B437" t="n">
-        <v>56.04</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="438">
@@ -13115,7 +13115,7 @@
         <v>46094</v>
       </c>
       <c r="B438" t="n">
-        <v>56.04</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="439">
@@ -13123,7 +13123,7 @@
         <v>46095</v>
       </c>
       <c r="B439" t="n">
-        <v>58.64</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="440">
@@ -13131,7 +13131,7 @@
         <v>46096</v>
       </c>
       <c r="B440" t="n">
-        <v>58.64</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="441">
@@ -13139,7 +13139,7 @@
         <v>46097</v>
       </c>
       <c r="B441" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="442">
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>57.23</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>56.33</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>56.33</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>56.33</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>56.33</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>56.33</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>55.73</v>
+        <v>46</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>55.85</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>54.91</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>52.56</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>51.8</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>51.35</v>
+        <v>45.62</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>51.2</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>47.25</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>35.98</v>
+        <v>31.97</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>38.44</v>
+        <v>34.09</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>26.09</v>
+        <v>24.94</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13107,7 +13107,7 @@
         <v>46093</v>
       </c>
       <c r="B437" t="n">
-        <v>46.47</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="438">
@@ -13115,7 +13115,7 @@
         <v>46094</v>
       </c>
       <c r="B438" t="n">
-        <v>46.47</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="439">
@@ -13123,7 +13123,7 @@
         <v>46095</v>
       </c>
       <c r="B439" t="n">
-        <v>48.1</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="440">
@@ -13131,7 +13131,7 @@
         <v>46096</v>
       </c>
       <c r="B440" t="n">
-        <v>48.1</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="441">
@@ -13139,7 +13139,7 @@
         <v>46097</v>
       </c>
       <c r="B441" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="442">
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>47.22</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>46.49</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>46.49</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>46.49</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>46.49</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>46.49</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>46.28</v>
+        <v>48.79</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>46.32</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>46.44</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>45.94</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>45.62</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>44.8</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>39.83</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>31.97</v>
+        <v>32.53</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>34.09</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>24.94</v>
+        <v>25.29</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13115,7 +13115,7 @@
         <v>46094</v>
       </c>
       <c r="B438" t="n">
-        <v>48.62</v>
+        <v>48.73</v>
       </c>
     </row>
     <row r="439">
@@ -13123,7 +13123,7 @@
         <v>46095</v>
       </c>
       <c r="B439" t="n">
-        <v>46.93</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="440">
@@ -13131,7 +13131,7 @@
         <v>46096</v>
       </c>
       <c r="B440" t="n">
-        <v>46.93</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="441">
@@ -13139,7 +13139,7 @@
         <v>46097</v>
       </c>
       <c r="B441" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="442">
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>49.28</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>49.11</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>49.11</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>49.11</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>49.11</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>49.11</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>49</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>48.79</v>
+        <v>50.16</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>48.41</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>47.62</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>47.22</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>46.88</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>45.9</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>44.22</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>32.53</v>
+        <v>33.41</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>35.14</v>
+        <v>36.15</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>25.29</v>
+        <v>25.85</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13123,7 +13123,7 @@
         <v>46095</v>
       </c>
       <c r="B439" t="n">
-        <v>50.25</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="440">
@@ -13131,7 +13131,7 @@
         <v>46096</v>
       </c>
       <c r="B440" t="n">
-        <v>50.25</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="441">
@@ -13139,7 +13139,7 @@
         <v>46097</v>
       </c>
       <c r="B441" t="n">
-        <v>49.74</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="442">
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>49.74</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>49.74</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>49.74</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>49.74</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>49.74</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>49.74</v>
+        <v>47.56</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>49.74</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>49.74</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>49.74</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>49.74</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>49.74</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>49.74</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>49.74</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>49.88</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>49.88</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>49.88</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>49.88</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>49.88</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>49.98</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>50.16</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>49.82</v>
+        <v>48.92</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>48.83</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>48.53</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>47.32</v>
+        <v>46.87</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>45.71</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>33.41</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="1005">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>25.85</v>
+        <v>26.11</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13147,7 +13147,7 @@
         <v>46098</v>
       </c>
       <c r="B442" t="n">
-        <v>47.56</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="443">
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>47.56</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>47.56</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>47.56</v>
+        <v>49.28</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>47.56</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>47.56</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>47.67</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>47.67</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>47.67</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>47.67</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>47.67</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>47.67</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>47.67</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>48.63</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>48.63</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>48.63</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>48.63</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>48.63</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>49.27</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>49.05</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>48.92</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>48.5</v>
+        <v>49.22</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>48.25</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>48.01</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>46.87</v>
+        <v>47.74</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>45.11</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>33.59</v>
+        <v>34.52</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>36.15</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>26.11</v>
+        <v>26.37</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13155,7 +13155,7 @@
         <v>46099</v>
       </c>
       <c r="B443" t="n">
-        <v>49.28</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="444">
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>49.28</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>49.28</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>49.8</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>49.8</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>49.68</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>49.68</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>49.68</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>49.68</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>49.68</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>49.68</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>49.68</v>
+        <v>50.92</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>49.82</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>49.82</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>49.82</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>49.82</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>49.82</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>49.92</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>50.07</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>49.65</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>49.22</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>48.98</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>48.8</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>47.74</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>45.94</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="868">
@@ -16555,7 +16555,7 @@
         <v>46524</v>
       </c>
       <c r="B868" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="869">
@@ -16563,7 +16563,7 @@
         <v>46525</v>
       </c>
       <c r="B869" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="870">
@@ -16571,7 +16571,7 @@
         <v>46526</v>
       </c>
       <c r="B870" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="871">
@@ -16579,7 +16579,7 @@
         <v>46527</v>
       </c>
       <c r="B871" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="872">
@@ -16587,7 +16587,7 @@
         <v>46528</v>
       </c>
       <c r="B872" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="873">
@@ -16595,7 +16595,7 @@
         <v>46529</v>
       </c>
       <c r="B873" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="874">
@@ -16603,7 +16603,7 @@
         <v>46530</v>
       </c>
       <c r="B874" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="875">
@@ -16611,7 +16611,7 @@
         <v>46531</v>
       </c>
       <c r="B875" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="876">
@@ -16619,7 +16619,7 @@
         <v>46532</v>
       </c>
       <c r="B876" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="877">
@@ -16627,7 +16627,7 @@
         <v>46533</v>
       </c>
       <c r="B877" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="878">
@@ -16635,7 +16635,7 @@
         <v>46534</v>
       </c>
       <c r="B878" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="879">
@@ -16643,7 +16643,7 @@
         <v>46535</v>
       </c>
       <c r="B879" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="880">
@@ -16651,7 +16651,7 @@
         <v>46536</v>
       </c>
       <c r="B880" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="881">
@@ -16659,7 +16659,7 @@
         <v>46537</v>
       </c>
       <c r="B881" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="882">
@@ -16667,7 +16667,7 @@
         <v>46538</v>
       </c>
       <c r="B882" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="883">
@@ -16675,7 +16675,7 @@
         <v>46539</v>
       </c>
       <c r="B883" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="884">
@@ -16683,7 +16683,7 @@
         <v>46540</v>
       </c>
       <c r="B884" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="885">
@@ -16691,7 +16691,7 @@
         <v>46541</v>
       </c>
       <c r="B885" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="886">
@@ -16699,7 +16699,7 @@
         <v>46542</v>
       </c>
       <c r="B886" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="887">
@@ -16707,7 +16707,7 @@
         <v>46543</v>
       </c>
       <c r="B887" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="888">
@@ -16715,7 +16715,7 @@
         <v>46544</v>
       </c>
       <c r="B888" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="889">
@@ -16723,7 +16723,7 @@
         <v>46545</v>
       </c>
       <c r="B889" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="890">
@@ -16731,7 +16731,7 @@
         <v>46546</v>
       </c>
       <c r="B890" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="891">
@@ -16739,7 +16739,7 @@
         <v>46547</v>
       </c>
       <c r="B891" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="892">
@@ -16747,7 +16747,7 @@
         <v>46548</v>
       </c>
       <c r="B892" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="893">
@@ -16755,7 +16755,7 @@
         <v>46549</v>
       </c>
       <c r="B893" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="894">
@@ -16763,7 +16763,7 @@
         <v>46550</v>
       </c>
       <c r="B894" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="895">
@@ -16771,7 +16771,7 @@
         <v>46551</v>
       </c>
       <c r="B895" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="896">
@@ -16779,7 +16779,7 @@
         <v>46552</v>
       </c>
       <c r="B896" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="897">
@@ -16787,7 +16787,7 @@
         <v>46553</v>
       </c>
       <c r="B897" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="898">
@@ -16795,7 +16795,7 @@
         <v>46554</v>
       </c>
       <c r="B898" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="899">
@@ -16803,7 +16803,7 @@
         <v>46555</v>
       </c>
       <c r="B899" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="900">
@@ -16811,7 +16811,7 @@
         <v>46556</v>
       </c>
       <c r="B900" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="901">
@@ -16819,7 +16819,7 @@
         <v>46557</v>
       </c>
       <c r="B901" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="902">
@@ -16827,7 +16827,7 @@
         <v>46558</v>
       </c>
       <c r="B902" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="903">
@@ -16835,7 +16835,7 @@
         <v>46559</v>
       </c>
       <c r="B903" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="904">
@@ -16843,7 +16843,7 @@
         <v>46560</v>
       </c>
       <c r="B904" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="905">
@@ -16851,7 +16851,7 @@
         <v>46561</v>
       </c>
       <c r="B905" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="906">
@@ -16859,7 +16859,7 @@
         <v>46562</v>
       </c>
       <c r="B906" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="907">
@@ -16867,7 +16867,7 @@
         <v>46563</v>
       </c>
       <c r="B907" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="908">
@@ -16875,7 +16875,7 @@
         <v>46564</v>
       </c>
       <c r="B908" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="909">
@@ -16883,7 +16883,7 @@
         <v>46565</v>
       </c>
       <c r="B909" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="910">
@@ -16891,7 +16891,7 @@
         <v>46566</v>
       </c>
       <c r="B910" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="911">
@@ -16899,7 +16899,7 @@
         <v>46567</v>
       </c>
       <c r="B911" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="912">
@@ -16907,7 +16907,7 @@
         <v>46568</v>
       </c>
       <c r="B912" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="913">
@@ -16915,7 +16915,7 @@
         <v>46569</v>
       </c>
       <c r="B913" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="914">
@@ -16923,7 +16923,7 @@
         <v>46570</v>
       </c>
       <c r="B914" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="915">
@@ -16931,7 +16931,7 @@
         <v>46571</v>
       </c>
       <c r="B915" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="916">
@@ -16939,7 +16939,7 @@
         <v>46572</v>
       </c>
       <c r="B916" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="917">
@@ -16947,7 +16947,7 @@
         <v>46573</v>
       </c>
       <c r="B917" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="918">
@@ -16955,7 +16955,7 @@
         <v>46574</v>
       </c>
       <c r="B918" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="919">
@@ -16963,7 +16963,7 @@
         <v>46575</v>
       </c>
       <c r="B919" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="920">
@@ -16971,7 +16971,7 @@
         <v>46576</v>
       </c>
       <c r="B920" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="921">
@@ -16979,7 +16979,7 @@
         <v>46577</v>
       </c>
       <c r="B921" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="922">
@@ -16987,7 +16987,7 @@
         <v>46578</v>
       </c>
       <c r="B922" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="923">
@@ -16995,7 +16995,7 @@
         <v>46579</v>
       </c>
       <c r="B923" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="924">
@@ -17003,7 +17003,7 @@
         <v>46580</v>
       </c>
       <c r="B924" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="925">
@@ -17011,7 +17011,7 @@
         <v>46581</v>
       </c>
       <c r="B925" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="926">
@@ -17019,7 +17019,7 @@
         <v>46582</v>
       </c>
       <c r="B926" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="927">
@@ -17027,7 +17027,7 @@
         <v>46583</v>
       </c>
       <c r="B927" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="928">
@@ -17035,7 +17035,7 @@
         <v>46584</v>
       </c>
       <c r="B928" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="929">
@@ -17043,7 +17043,7 @@
         <v>46585</v>
       </c>
       <c r="B929" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="930">
@@ -17051,7 +17051,7 @@
         <v>46586</v>
       </c>
       <c r="B930" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="931">
@@ -17059,7 +17059,7 @@
         <v>46587</v>
       </c>
       <c r="B931" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="932">
@@ -17067,7 +17067,7 @@
         <v>46588</v>
       </c>
       <c r="B932" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="933">
@@ -17075,7 +17075,7 @@
         <v>46589</v>
       </c>
       <c r="B933" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="934">
@@ -17083,7 +17083,7 @@
         <v>46590</v>
       </c>
       <c r="B934" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="935">
@@ -17091,7 +17091,7 @@
         <v>46591</v>
       </c>
       <c r="B935" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="936">
@@ -17099,7 +17099,7 @@
         <v>46592</v>
       </c>
       <c r="B936" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="937">
@@ -17107,7 +17107,7 @@
         <v>46593</v>
       </c>
       <c r="B937" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="938">
@@ -17115,7 +17115,7 @@
         <v>46594</v>
       </c>
       <c r="B938" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="939">
@@ -17123,7 +17123,7 @@
         <v>46595</v>
       </c>
       <c r="B939" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="940">
@@ -17131,7 +17131,7 @@
         <v>46596</v>
       </c>
       <c r="B940" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="941">
@@ -17139,7 +17139,7 @@
         <v>46597</v>
       </c>
       <c r="B941" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="942">
@@ -17147,7 +17147,7 @@
         <v>46598</v>
       </c>
       <c r="B942" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="943">
@@ -17155,7 +17155,7 @@
         <v>46599</v>
       </c>
       <c r="B943" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="944">
@@ -17163,7 +17163,7 @@
         <v>46600</v>
       </c>
       <c r="B944" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="945">
@@ -17171,7 +17171,7 @@
         <v>46601</v>
       </c>
       <c r="B945" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="946">
@@ -17179,7 +17179,7 @@
         <v>46602</v>
       </c>
       <c r="B946" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="947">
@@ -17187,7 +17187,7 @@
         <v>46603</v>
       </c>
       <c r="B947" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="948">
@@ -17195,7 +17195,7 @@
         <v>46604</v>
       </c>
       <c r="B948" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="949">
@@ -17203,7 +17203,7 @@
         <v>46605</v>
       </c>
       <c r="B949" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="950">
@@ -17211,7 +17211,7 @@
         <v>46606</v>
       </c>
       <c r="B950" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="951">
@@ -17219,7 +17219,7 @@
         <v>46607</v>
       </c>
       <c r="B951" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="952">
@@ -17227,7 +17227,7 @@
         <v>46608</v>
       </c>
       <c r="B952" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="953">
@@ -17235,7 +17235,7 @@
         <v>46609</v>
       </c>
       <c r="B953" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="954">
@@ -17243,7 +17243,7 @@
         <v>46610</v>
       </c>
       <c r="B954" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="955">
@@ -17251,7 +17251,7 @@
         <v>46611</v>
       </c>
       <c r="B955" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="956">
@@ -17259,7 +17259,7 @@
         <v>46612</v>
       </c>
       <c r="B956" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="957">
@@ -17267,7 +17267,7 @@
         <v>46613</v>
       </c>
       <c r="B957" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="958">
@@ -17275,7 +17275,7 @@
         <v>46614</v>
       </c>
       <c r="B958" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="959">
@@ -17283,7 +17283,7 @@
         <v>46615</v>
       </c>
       <c r="B959" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="960">
@@ -17291,7 +17291,7 @@
         <v>46616</v>
       </c>
       <c r="B960" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="961">
@@ -17299,7 +17299,7 @@
         <v>46617</v>
       </c>
       <c r="B961" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="962">
@@ -17307,7 +17307,7 @@
         <v>46618</v>
       </c>
       <c r="B962" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="963">
@@ -17315,7 +17315,7 @@
         <v>46619</v>
       </c>
       <c r="B963" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="964">
@@ -17323,7 +17323,7 @@
         <v>46620</v>
       </c>
       <c r="B964" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="965">
@@ -17331,7 +17331,7 @@
         <v>46621</v>
       </c>
       <c r="B965" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="966">
@@ -17339,7 +17339,7 @@
         <v>46622</v>
       </c>
       <c r="B966" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="967">
@@ -17347,7 +17347,7 @@
         <v>46623</v>
       </c>
       <c r="B967" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="968">
@@ -17355,7 +17355,7 @@
         <v>46624</v>
       </c>
       <c r="B968" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="969">
@@ -17363,7 +17363,7 @@
         <v>46625</v>
       </c>
       <c r="B969" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="970">
@@ -17371,7 +17371,7 @@
         <v>46626</v>
       </c>
       <c r="B970" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="971">
@@ -17379,7 +17379,7 @@
         <v>46627</v>
       </c>
       <c r="B971" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="972">
@@ -17387,7 +17387,7 @@
         <v>46628</v>
       </c>
       <c r="B972" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="973">
@@ -17395,7 +17395,7 @@
         <v>46629</v>
       </c>
       <c r="B973" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="974">
@@ -17403,7 +17403,7 @@
         <v>46630</v>
       </c>
       <c r="B974" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="975">
@@ -17411,7 +17411,7 @@
         <v>46631</v>
       </c>
       <c r="B975" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="976">
@@ -17419,7 +17419,7 @@
         <v>46632</v>
       </c>
       <c r="B976" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="977">
@@ -17427,7 +17427,7 @@
         <v>46633</v>
       </c>
       <c r="B977" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="978">
@@ -17435,7 +17435,7 @@
         <v>46634</v>
       </c>
       <c r="B978" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="979">
@@ -17443,7 +17443,7 @@
         <v>46635</v>
       </c>
       <c r="B979" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="980">
@@ -17451,7 +17451,7 @@
         <v>46636</v>
       </c>
       <c r="B980" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="981">
@@ -17459,7 +17459,7 @@
         <v>46637</v>
       </c>
       <c r="B981" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="982">
@@ -17467,7 +17467,7 @@
         <v>46638</v>
       </c>
       <c r="B982" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="983">
@@ -17475,7 +17475,7 @@
         <v>46639</v>
       </c>
       <c r="B983" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="984">
@@ -17483,7 +17483,7 @@
         <v>46640</v>
       </c>
       <c r="B984" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="985">
@@ -17491,7 +17491,7 @@
         <v>46641</v>
       </c>
       <c r="B985" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="986">
@@ -17499,7 +17499,7 @@
         <v>46642</v>
       </c>
       <c r="B986" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="987">
@@ -17507,7 +17507,7 @@
         <v>46643</v>
       </c>
       <c r="B987" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="988">
@@ -17515,7 +17515,7 @@
         <v>46644</v>
       </c>
       <c r="B988" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="989">
@@ -17523,7 +17523,7 @@
         <v>46645</v>
       </c>
       <c r="B989" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="990">
@@ -17531,7 +17531,7 @@
         <v>46646</v>
       </c>
       <c r="B990" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="991">
@@ -17539,7 +17539,7 @@
         <v>46647</v>
       </c>
       <c r="B991" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="992">
@@ -17547,7 +17547,7 @@
         <v>46648</v>
       </c>
       <c r="B992" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="993">
@@ -17555,7 +17555,7 @@
         <v>46649</v>
       </c>
       <c r="B993" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="994">
@@ -17563,7 +17563,7 @@
         <v>46650</v>
       </c>
       <c r="B994" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="995">
@@ -17571,7 +17571,7 @@
         <v>46651</v>
       </c>
       <c r="B995" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="996">
@@ -17579,7 +17579,7 @@
         <v>46652</v>
       </c>
       <c r="B996" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="997">
@@ -17587,7 +17587,7 @@
         <v>46653</v>
       </c>
       <c r="B997" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="998">
@@ -17595,7 +17595,7 @@
         <v>46654</v>
       </c>
       <c r="B998" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="999">
@@ -17603,7 +17603,7 @@
         <v>46655</v>
       </c>
       <c r="B999" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1000">
@@ -17611,7 +17611,7 @@
         <v>46656</v>
       </c>
       <c r="B1000" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1001">
@@ -17619,7 +17619,7 @@
         <v>46657</v>
       </c>
       <c r="B1001" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1002">
@@ -17627,7 +17627,7 @@
         <v>46658</v>
       </c>
       <c r="B1002" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1003">
@@ -17635,7 +17635,7 @@
         <v>46659</v>
       </c>
       <c r="B1003" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1004">
@@ -17643,7 +17643,7 @@
         <v>46660</v>
       </c>
       <c r="B1004" t="n">
-        <v>34.52</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="1005">
@@ -17651,7 +17651,7 @@
         <v>46661</v>
       </c>
       <c r="B1005" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1006">
@@ -17659,7 +17659,7 @@
         <v>46662</v>
       </c>
       <c r="B1006" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1007">
@@ -17667,7 +17667,7 @@
         <v>46663</v>
       </c>
       <c r="B1007" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1008">
@@ -17675,7 +17675,7 @@
         <v>46664</v>
       </c>
       <c r="B1008" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1009">
@@ -17683,7 +17683,7 @@
         <v>46665</v>
       </c>
       <c r="B1009" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1010">
@@ -17691,7 +17691,7 @@
         <v>46666</v>
       </c>
       <c r="B1010" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1011">
@@ -17699,7 +17699,7 @@
         <v>46667</v>
       </c>
       <c r="B1011" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1012">
@@ -17707,7 +17707,7 @@
         <v>46668</v>
       </c>
       <c r="B1012" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1013">
@@ -17715,7 +17715,7 @@
         <v>46669</v>
       </c>
       <c r="B1013" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1014">
@@ -17723,7 +17723,7 @@
         <v>46670</v>
       </c>
       <c r="B1014" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1015">
@@ -17731,7 +17731,7 @@
         <v>46671</v>
       </c>
       <c r="B1015" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1016">
@@ -17739,7 +17739,7 @@
         <v>46672</v>
       </c>
       <c r="B1016" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1017">
@@ -17747,7 +17747,7 @@
         <v>46673</v>
       </c>
       <c r="B1017" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1018">
@@ -17755,7 +17755,7 @@
         <v>46674</v>
       </c>
       <c r="B1018" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1019">
@@ -17763,7 +17763,7 @@
         <v>46675</v>
       </c>
       <c r="B1019" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1020">
@@ -17771,7 +17771,7 @@
         <v>46676</v>
       </c>
       <c r="B1020" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1021">
@@ -17779,7 +17779,7 @@
         <v>46677</v>
       </c>
       <c r="B1021" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1022">
@@ -17787,7 +17787,7 @@
         <v>46678</v>
       </c>
       <c r="B1022" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1023">
@@ -17795,7 +17795,7 @@
         <v>46679</v>
       </c>
       <c r="B1023" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1024">
@@ -17803,7 +17803,7 @@
         <v>46680</v>
       </c>
       <c r="B1024" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1025">
@@ -17811,7 +17811,7 @@
         <v>46681</v>
       </c>
       <c r="B1025" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1026">
@@ -17819,7 +17819,7 @@
         <v>46682</v>
       </c>
       <c r="B1026" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1027">
@@ -17827,7 +17827,7 @@
         <v>46683</v>
       </c>
       <c r="B1027" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1028">
@@ -17835,7 +17835,7 @@
         <v>46684</v>
       </c>
       <c r="B1028" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1029">
@@ -17843,7 +17843,7 @@
         <v>46685</v>
       </c>
       <c r="B1029" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1030">
@@ -17851,7 +17851,7 @@
         <v>46686</v>
       </c>
       <c r="B1030" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1031">
@@ -17859,7 +17859,7 @@
         <v>46687</v>
       </c>
       <c r="B1031" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1032">
@@ -17867,7 +17867,7 @@
         <v>46688</v>
       </c>
       <c r="B1032" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1033">
@@ -17875,7 +17875,7 @@
         <v>46689</v>
       </c>
       <c r="B1033" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1034">
@@ -17883,7 +17883,7 @@
         <v>46690</v>
       </c>
       <c r="B1034" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1035">
@@ -17891,7 +17891,7 @@
         <v>46691</v>
       </c>
       <c r="B1035" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1036">
@@ -17899,7 +17899,7 @@
         <v>46692</v>
       </c>
       <c r="B1036" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1037">
@@ -17907,7 +17907,7 @@
         <v>46693</v>
       </c>
       <c r="B1037" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1038">
@@ -17915,7 +17915,7 @@
         <v>46694</v>
       </c>
       <c r="B1038" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1039">
@@ -17923,7 +17923,7 @@
         <v>46695</v>
       </c>
       <c r="B1039" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1040">
@@ -17931,7 +17931,7 @@
         <v>46696</v>
       </c>
       <c r="B1040" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1041">
@@ -17939,7 +17939,7 @@
         <v>46697</v>
       </c>
       <c r="B1041" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1042">
@@ -17947,7 +17947,7 @@
         <v>46698</v>
       </c>
       <c r="B1042" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1043">
@@ -17955,7 +17955,7 @@
         <v>46699</v>
       </c>
       <c r="B1043" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1044">
@@ -17963,7 +17963,7 @@
         <v>46700</v>
       </c>
       <c r="B1044" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1045">
@@ -17971,7 +17971,7 @@
         <v>46701</v>
       </c>
       <c r="B1045" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1046">
@@ -17979,7 +17979,7 @@
         <v>46702</v>
       </c>
       <c r="B1046" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1047">
@@ -17987,7 +17987,7 @@
         <v>46703</v>
       </c>
       <c r="B1047" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1048">
@@ -17995,7 +17995,7 @@
         <v>46704</v>
       </c>
       <c r="B1048" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1049">
@@ -18003,7 +18003,7 @@
         <v>46705</v>
       </c>
       <c r="B1049" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1050">
@@ -18011,7 +18011,7 @@
         <v>46706</v>
       </c>
       <c r="B1050" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1051">
@@ -18019,7 +18019,7 @@
         <v>46707</v>
       </c>
       <c r="B1051" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1052">
@@ -18027,7 +18027,7 @@
         <v>46708</v>
       </c>
       <c r="B1052" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1053">
@@ -18035,7 +18035,7 @@
         <v>46709</v>
       </c>
       <c r="B1053" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1054">
@@ -18043,7 +18043,7 @@
         <v>46710</v>
       </c>
       <c r="B1054" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1055">
@@ -18051,7 +18051,7 @@
         <v>46711</v>
       </c>
       <c r="B1055" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1056">
@@ -18059,7 +18059,7 @@
         <v>46712</v>
       </c>
       <c r="B1056" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1057">
@@ -18067,7 +18067,7 @@
         <v>46713</v>
       </c>
       <c r="B1057" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1058">
@@ -18075,7 +18075,7 @@
         <v>46714</v>
       </c>
       <c r="B1058" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1059">
@@ -18083,7 +18083,7 @@
         <v>46715</v>
       </c>
       <c r="B1059" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1060">
@@ -18091,7 +18091,7 @@
         <v>46716</v>
       </c>
       <c r="B1060" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1061">
@@ -18099,7 +18099,7 @@
         <v>46717</v>
       </c>
       <c r="B1061" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1062">
@@ -18107,7 +18107,7 @@
         <v>46718</v>
       </c>
       <c r="B1062" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1063">
@@ -18115,7 +18115,7 @@
         <v>46719</v>
       </c>
       <c r="B1063" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1064">
@@ -18123,7 +18123,7 @@
         <v>46720</v>
       </c>
       <c r="B1064" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1065">
@@ -18131,7 +18131,7 @@
         <v>46721</v>
       </c>
       <c r="B1065" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1066">
@@ -18139,7 +18139,7 @@
         <v>46722</v>
       </c>
       <c r="B1066" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1067">
@@ -18147,7 +18147,7 @@
         <v>46723</v>
       </c>
       <c r="B1067" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1068">
@@ -18155,7 +18155,7 @@
         <v>46724</v>
       </c>
       <c r="B1068" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1069">
@@ -18163,7 +18163,7 @@
         <v>46725</v>
       </c>
       <c r="B1069" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1070">
@@ -18171,7 +18171,7 @@
         <v>46726</v>
       </c>
       <c r="B1070" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1071">
@@ -18179,7 +18179,7 @@
         <v>46727</v>
       </c>
       <c r="B1071" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1072">
@@ -18187,7 +18187,7 @@
         <v>46728</v>
       </c>
       <c r="B1072" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1073">
@@ -18195,7 +18195,7 @@
         <v>46729</v>
       </c>
       <c r="B1073" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1074">
@@ -18203,7 +18203,7 @@
         <v>46730</v>
       </c>
       <c r="B1074" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1075">
@@ -18211,7 +18211,7 @@
         <v>46731</v>
       </c>
       <c r="B1075" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1076">
@@ -18219,7 +18219,7 @@
         <v>46732</v>
       </c>
       <c r="B1076" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1077">
@@ -18227,7 +18227,7 @@
         <v>46733</v>
       </c>
       <c r="B1077" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1078">
@@ -18235,7 +18235,7 @@
         <v>46734</v>
       </c>
       <c r="B1078" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1079">
@@ -18243,7 +18243,7 @@
         <v>46735</v>
       </c>
       <c r="B1079" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1080">
@@ -18251,7 +18251,7 @@
         <v>46736</v>
       </c>
       <c r="B1080" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1081">
@@ -18259,7 +18259,7 @@
         <v>46737</v>
       </c>
       <c r="B1081" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1082">
@@ -18267,7 +18267,7 @@
         <v>46738</v>
       </c>
       <c r="B1082" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1083">
@@ -18275,7 +18275,7 @@
         <v>46739</v>
       </c>
       <c r="B1083" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1084">
@@ -18283,7 +18283,7 @@
         <v>46740</v>
       </c>
       <c r="B1084" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1085">
@@ -18291,7 +18291,7 @@
         <v>46741</v>
       </c>
       <c r="B1085" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1086">
@@ -18299,7 +18299,7 @@
         <v>46742</v>
       </c>
       <c r="B1086" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1087">
@@ -18307,7 +18307,7 @@
         <v>46743</v>
       </c>
       <c r="B1087" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1088">
@@ -18315,7 +18315,7 @@
         <v>46744</v>
       </c>
       <c r="B1088" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1089">
@@ -18323,7 +18323,7 @@
         <v>46745</v>
       </c>
       <c r="B1089" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1090">
@@ -18331,7 +18331,7 @@
         <v>46746</v>
       </c>
       <c r="B1090" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1091">
@@ -18339,7 +18339,7 @@
         <v>46747</v>
       </c>
       <c r="B1091" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1092">
@@ -18347,7 +18347,7 @@
         <v>46748</v>
       </c>
       <c r="B1092" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1093">
@@ -18355,7 +18355,7 @@
         <v>46749</v>
       </c>
       <c r="B1093" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1094">
@@ -18363,7 +18363,7 @@
         <v>46750</v>
       </c>
       <c r="B1094" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1095">
@@ -18371,7 +18371,7 @@
         <v>46751</v>
       </c>
       <c r="B1095" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1096">
@@ -18379,7 +18379,7 @@
         <v>46752</v>
       </c>
       <c r="B1096" t="n">
-        <v>36.98</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="1097">
@@ -18387,7 +18387,7 @@
         <v>46753</v>
       </c>
       <c r="B1097" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1098">
@@ -18395,7 +18395,7 @@
         <v>46754</v>
       </c>
       <c r="B1098" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1099">
@@ -18403,7 +18403,7 @@
         <v>46755</v>
       </c>
       <c r="B1099" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1100">
@@ -18411,7 +18411,7 @@
         <v>46756</v>
       </c>
       <c r="B1100" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1101">
@@ -18419,7 +18419,7 @@
         <v>46757</v>
       </c>
       <c r="B1101" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1102">
@@ -18427,7 +18427,7 @@
         <v>46758</v>
       </c>
       <c r="B1102" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1103">
@@ -18435,7 +18435,7 @@
         <v>46759</v>
       </c>
       <c r="B1103" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1104">
@@ -18443,7 +18443,7 @@
         <v>46760</v>
       </c>
       <c r="B1104" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1105">
@@ -18451,7 +18451,7 @@
         <v>46761</v>
       </c>
       <c r="B1105" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1106">
@@ -18459,7 +18459,7 @@
         <v>46762</v>
       </c>
       <c r="B1106" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1107">
@@ -18467,7 +18467,7 @@
         <v>46763</v>
       </c>
       <c r="B1107" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1108">
@@ -18475,7 +18475,7 @@
         <v>46764</v>
       </c>
       <c r="B1108" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1109">
@@ -18483,7 +18483,7 @@
         <v>46765</v>
       </c>
       <c r="B1109" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1110">
@@ -18491,7 +18491,7 @@
         <v>46766</v>
       </c>
       <c r="B1110" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1111">
@@ -18499,7 +18499,7 @@
         <v>46767</v>
       </c>
       <c r="B1111" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1112">
@@ -18507,7 +18507,7 @@
         <v>46768</v>
       </c>
       <c r="B1112" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1113">
@@ -18515,7 +18515,7 @@
         <v>46769</v>
       </c>
       <c r="B1113" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1114">
@@ -18523,7 +18523,7 @@
         <v>46770</v>
       </c>
       <c r="B1114" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1115">
@@ -18531,7 +18531,7 @@
         <v>46771</v>
       </c>
       <c r="B1115" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1116">
@@ -18539,7 +18539,7 @@
         <v>46772</v>
       </c>
       <c r="B1116" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1117">
@@ -18547,7 +18547,7 @@
         <v>46773</v>
       </c>
       <c r="B1117" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1118">
@@ -18555,7 +18555,7 @@
         <v>46774</v>
       </c>
       <c r="B1118" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1119">
@@ -18563,7 +18563,7 @@
         <v>46775</v>
       </c>
       <c r="B1119" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1120">
@@ -18571,7 +18571,7 @@
         <v>46776</v>
       </c>
       <c r="B1120" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1121">
@@ -18579,7 +18579,7 @@
         <v>46777</v>
       </c>
       <c r="B1121" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1122">
@@ -18587,7 +18587,7 @@
         <v>46778</v>
       </c>
       <c r="B1122" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1123">
@@ -18595,7 +18595,7 @@
         <v>46779</v>
       </c>
       <c r="B1123" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1124">
@@ -18603,7 +18603,7 @@
         <v>46780</v>
       </c>
       <c r="B1124" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1125">
@@ -18611,7 +18611,7 @@
         <v>46781</v>
       </c>
       <c r="B1125" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1126">
@@ -18619,7 +18619,7 @@
         <v>46782</v>
       </c>
       <c r="B1126" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1127">
@@ -18627,7 +18627,7 @@
         <v>46783</v>
       </c>
       <c r="B1127" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1128">
@@ -18635,7 +18635,7 @@
         <v>46784</v>
       </c>
       <c r="B1128" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1129">
@@ -18643,7 +18643,7 @@
         <v>46785</v>
       </c>
       <c r="B1129" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1130">
@@ -18651,7 +18651,7 @@
         <v>46786</v>
       </c>
       <c r="B1130" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1131">
@@ -18659,7 +18659,7 @@
         <v>46787</v>
       </c>
       <c r="B1131" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1132">
@@ -18667,7 +18667,7 @@
         <v>46788</v>
       </c>
       <c r="B1132" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1133">
@@ -18675,7 +18675,7 @@
         <v>46789</v>
       </c>
       <c r="B1133" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1134">
@@ -18683,7 +18683,7 @@
         <v>46790</v>
       </c>
       <c r="B1134" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1135">
@@ -18691,7 +18691,7 @@
         <v>46791</v>
       </c>
       <c r="B1135" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1136">
@@ -18699,7 +18699,7 @@
         <v>46792</v>
       </c>
       <c r="B1136" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1137">
@@ -18707,7 +18707,7 @@
         <v>46793</v>
       </c>
       <c r="B1137" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1138">
@@ -18715,7 +18715,7 @@
         <v>46794</v>
       </c>
       <c r="B1138" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1139">
@@ -18723,7 +18723,7 @@
         <v>46795</v>
       </c>
       <c r="B1139" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1140">
@@ -18731,7 +18731,7 @@
         <v>46796</v>
       </c>
       <c r="B1140" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1141">
@@ -18739,7 +18739,7 @@
         <v>46797</v>
       </c>
       <c r="B1141" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1142">
@@ -18747,7 +18747,7 @@
         <v>46798</v>
       </c>
       <c r="B1142" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1143">
@@ -18755,7 +18755,7 @@
         <v>46799</v>
       </c>
       <c r="B1143" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1144">
@@ -18763,7 +18763,7 @@
         <v>46800</v>
       </c>
       <c r="B1144" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1145">
@@ -18771,7 +18771,7 @@
         <v>46801</v>
       </c>
       <c r="B1145" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1146">
@@ -18779,7 +18779,7 @@
         <v>46802</v>
       </c>
       <c r="B1146" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1147">
@@ -18787,7 +18787,7 @@
         <v>46803</v>
       </c>
       <c r="B1147" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1148">
@@ -18795,7 +18795,7 @@
         <v>46804</v>
       </c>
       <c r="B1148" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1149">
@@ -18803,7 +18803,7 @@
         <v>46805</v>
       </c>
       <c r="B1149" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1150">
@@ -18811,7 +18811,7 @@
         <v>46806</v>
       </c>
       <c r="B1150" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1151">
@@ -18819,7 +18819,7 @@
         <v>46807</v>
       </c>
       <c r="B1151" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1152">
@@ -18827,7 +18827,7 @@
         <v>46808</v>
       </c>
       <c r="B1152" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1153">
@@ -18835,7 +18835,7 @@
         <v>46809</v>
       </c>
       <c r="B1153" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1154">
@@ -18843,7 +18843,7 @@
         <v>46810</v>
       </c>
       <c r="B1154" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1155">
@@ -18851,7 +18851,7 @@
         <v>46811</v>
       </c>
       <c r="B1155" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1156">
@@ -18859,7 +18859,7 @@
         <v>46812</v>
       </c>
       <c r="B1156" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1157">
@@ -18867,7 +18867,7 @@
         <v>46813</v>
       </c>
       <c r="B1157" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1158">
@@ -18875,7 +18875,7 @@
         <v>46814</v>
       </c>
       <c r="B1158" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1159">
@@ -18883,7 +18883,7 @@
         <v>46815</v>
       </c>
       <c r="B1159" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1160">
@@ -18891,7 +18891,7 @@
         <v>46816</v>
       </c>
       <c r="B1160" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1161">
@@ -18899,7 +18899,7 @@
         <v>46817</v>
       </c>
       <c r="B1161" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1162">
@@ -18907,7 +18907,7 @@
         <v>46818</v>
       </c>
       <c r="B1162" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1163">
@@ -18915,7 +18915,7 @@
         <v>46819</v>
       </c>
       <c r="B1163" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1164">
@@ -18923,7 +18923,7 @@
         <v>46820</v>
       </c>
       <c r="B1164" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1165">
@@ -18931,7 +18931,7 @@
         <v>46821</v>
       </c>
       <c r="B1165" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1166">
@@ -18939,7 +18939,7 @@
         <v>46822</v>
       </c>
       <c r="B1166" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1167">
@@ -18947,7 +18947,7 @@
         <v>46823</v>
       </c>
       <c r="B1167" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1168">
@@ -18955,7 +18955,7 @@
         <v>46824</v>
       </c>
       <c r="B1168" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1169">
@@ -18963,7 +18963,7 @@
         <v>46825</v>
       </c>
       <c r="B1169" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1170">
@@ -18971,7 +18971,7 @@
         <v>46826</v>
       </c>
       <c r="B1170" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1171">
@@ -18979,7 +18979,7 @@
         <v>46827</v>
       </c>
       <c r="B1171" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1172">
@@ -18987,7 +18987,7 @@
         <v>46828</v>
       </c>
       <c r="B1172" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1173">
@@ -18995,7 +18995,7 @@
         <v>46829</v>
       </c>
       <c r="B1173" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1174">
@@ -19003,7 +19003,7 @@
         <v>46830</v>
       </c>
       <c r="B1174" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1175">
@@ -19011,7 +19011,7 @@
         <v>46831</v>
       </c>
       <c r="B1175" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1176">
@@ -19019,7 +19019,7 @@
         <v>46832</v>
       </c>
       <c r="B1176" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1177">
@@ -19027,7 +19027,7 @@
         <v>46833</v>
       </c>
       <c r="B1177" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1178">
@@ -19035,7 +19035,7 @@
         <v>46834</v>
       </c>
       <c r="B1178" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1179">
@@ -19043,7 +19043,7 @@
         <v>46835</v>
       </c>
       <c r="B1179" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1180">
@@ -19051,7 +19051,7 @@
         <v>46836</v>
       </c>
       <c r="B1180" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1181">
@@ -19059,7 +19059,7 @@
         <v>46837</v>
       </c>
       <c r="B1181" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1182">
@@ -19067,7 +19067,7 @@
         <v>46838</v>
       </c>
       <c r="B1182" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1183">
@@ -19075,7 +19075,7 @@
         <v>46839</v>
       </c>
       <c r="B1183" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1184">
@@ -19083,7 +19083,7 @@
         <v>46840</v>
       </c>
       <c r="B1184" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1185">
@@ -19091,7 +19091,7 @@
         <v>46841</v>
       </c>
       <c r="B1185" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1186">
@@ -19099,7 +19099,7 @@
         <v>46842</v>
       </c>
       <c r="B1186" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1187">
@@ -19107,7 +19107,7 @@
         <v>46843</v>
       </c>
       <c r="B1187" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1188">
@@ -19115,7 +19115,7 @@
         <v>46844</v>
       </c>
       <c r="B1188" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1189">
@@ -19123,7 +19123,7 @@
         <v>46845</v>
       </c>
       <c r="B1189" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1190">
@@ -19131,7 +19131,7 @@
         <v>46846</v>
       </c>
       <c r="B1190" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1191">
@@ -19139,7 +19139,7 @@
         <v>46847</v>
       </c>
       <c r="B1191" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1192">
@@ -19147,7 +19147,7 @@
         <v>46848</v>
       </c>
       <c r="B1192" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1193">
@@ -19155,7 +19155,7 @@
         <v>46849</v>
       </c>
       <c r="B1193" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1194">
@@ -19163,7 +19163,7 @@
         <v>46850</v>
       </c>
       <c r="B1194" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1195">
@@ -19171,7 +19171,7 @@
         <v>46851</v>
       </c>
       <c r="B1195" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1196">
@@ -19179,7 +19179,7 @@
         <v>46852</v>
       </c>
       <c r="B1196" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1197">
@@ -19187,7 +19187,7 @@
         <v>46853</v>
       </c>
       <c r="B1197" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1198">
@@ -19195,7 +19195,7 @@
         <v>46854</v>
       </c>
       <c r="B1198" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1199">
@@ -19203,7 +19203,7 @@
         <v>46855</v>
       </c>
       <c r="B1199" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1200">
@@ -19211,7 +19211,7 @@
         <v>46856</v>
       </c>
       <c r="B1200" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1201">
@@ -19219,7 +19219,7 @@
         <v>46857</v>
       </c>
       <c r="B1201" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1202">
@@ -19227,7 +19227,7 @@
         <v>46858</v>
       </c>
       <c r="B1202" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1203">
@@ -19235,7 +19235,7 @@
         <v>46859</v>
       </c>
       <c r="B1203" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1204">
@@ -19243,7 +19243,7 @@
         <v>46860</v>
       </c>
       <c r="B1204" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1205">
@@ -19251,7 +19251,7 @@
         <v>46861</v>
       </c>
       <c r="B1205" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1206">
@@ -19259,7 +19259,7 @@
         <v>46862</v>
       </c>
       <c r="B1206" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1207">
@@ -19267,7 +19267,7 @@
         <v>46863</v>
       </c>
       <c r="B1207" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1208">
@@ -19275,7 +19275,7 @@
         <v>46864</v>
       </c>
       <c r="B1208" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1209">
@@ -19283,7 +19283,7 @@
         <v>46865</v>
       </c>
       <c r="B1209" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1210">
@@ -19291,7 +19291,7 @@
         <v>46866</v>
       </c>
       <c r="B1210" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1211">
@@ -19299,7 +19299,7 @@
         <v>46867</v>
       </c>
       <c r="B1211" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1212">
@@ -19307,7 +19307,7 @@
         <v>46868</v>
       </c>
       <c r="B1212" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1213">
@@ -19315,7 +19315,7 @@
         <v>46869</v>
       </c>
       <c r="B1213" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1214">
@@ -19323,7 +19323,7 @@
         <v>46870</v>
       </c>
       <c r="B1214" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1215">
@@ -19331,7 +19331,7 @@
         <v>46871</v>
       </c>
       <c r="B1215" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1216">
@@ -19339,7 +19339,7 @@
         <v>46872</v>
       </c>
       <c r="B1216" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1217">
@@ -19347,7 +19347,7 @@
         <v>46873</v>
       </c>
       <c r="B1217" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1218">
@@ -19355,7 +19355,7 @@
         <v>46874</v>
       </c>
       <c r="B1218" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1219">
@@ -19363,7 +19363,7 @@
         <v>46875</v>
       </c>
       <c r="B1219" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1220">
@@ -19371,7 +19371,7 @@
         <v>46876</v>
       </c>
       <c r="B1220" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1221">
@@ -19379,7 +19379,7 @@
         <v>46877</v>
       </c>
       <c r="B1221" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1222">
@@ -19387,7 +19387,7 @@
         <v>46878</v>
       </c>
       <c r="B1222" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1223">
@@ -19395,7 +19395,7 @@
         <v>46879</v>
       </c>
       <c r="B1223" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1224">
@@ -19403,7 +19403,7 @@
         <v>46880</v>
       </c>
       <c r="B1224" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1225">
@@ -19411,7 +19411,7 @@
         <v>46881</v>
       </c>
       <c r="B1225" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1226">
@@ -19419,7 +19419,7 @@
         <v>46882</v>
       </c>
       <c r="B1226" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1227">
@@ -19427,7 +19427,7 @@
         <v>46883</v>
       </c>
       <c r="B1227" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1228">
@@ -19435,7 +19435,7 @@
         <v>46884</v>
       </c>
       <c r="B1228" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1229">
@@ -19443,7 +19443,7 @@
         <v>46885</v>
       </c>
       <c r="B1229" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1230">
@@ -19451,7 +19451,7 @@
         <v>46886</v>
       </c>
       <c r="B1230" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1231">
@@ -19459,7 +19459,7 @@
         <v>46887</v>
       </c>
       <c r="B1231" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1232">
@@ -19467,7 +19467,7 @@
         <v>46888</v>
       </c>
       <c r="B1232" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1233">
@@ -19475,7 +19475,7 @@
         <v>46889</v>
       </c>
       <c r="B1233" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1234">
@@ -19483,7 +19483,7 @@
         <v>46890</v>
       </c>
       <c r="B1234" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1235">
@@ -19491,7 +19491,7 @@
         <v>46891</v>
       </c>
       <c r="B1235" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1236">
@@ -19499,7 +19499,7 @@
         <v>46892</v>
       </c>
       <c r="B1236" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1237">
@@ -19507,7 +19507,7 @@
         <v>46893</v>
       </c>
       <c r="B1237" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1238">
@@ -19515,7 +19515,7 @@
         <v>46894</v>
       </c>
       <c r="B1238" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1239">
@@ -19523,7 +19523,7 @@
         <v>46895</v>
       </c>
       <c r="B1239" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1240">
@@ -19531,7 +19531,7 @@
         <v>46896</v>
       </c>
       <c r="B1240" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1241">
@@ -19539,7 +19539,7 @@
         <v>46897</v>
       </c>
       <c r="B1241" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1242">
@@ -19547,7 +19547,7 @@
         <v>46898</v>
       </c>
       <c r="B1242" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1243">
@@ -19555,7 +19555,7 @@
         <v>46899</v>
       </c>
       <c r="B1243" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1244">
@@ -19563,7 +19563,7 @@
         <v>46900</v>
       </c>
       <c r="B1244" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1245">
@@ -19571,7 +19571,7 @@
         <v>46901</v>
       </c>
       <c r="B1245" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1246">
@@ -19579,7 +19579,7 @@
         <v>46902</v>
       </c>
       <c r="B1246" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1247">
@@ -19587,7 +19587,7 @@
         <v>46903</v>
       </c>
       <c r="B1247" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1248">
@@ -19595,7 +19595,7 @@
         <v>46904</v>
       </c>
       <c r="B1248" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1249">
@@ -19603,7 +19603,7 @@
         <v>46905</v>
       </c>
       <c r="B1249" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1250">
@@ -19611,7 +19611,7 @@
         <v>46906</v>
       </c>
       <c r="B1250" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1251">
@@ -19619,7 +19619,7 @@
         <v>46907</v>
       </c>
       <c r="B1251" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1252">
@@ -19627,7 +19627,7 @@
         <v>46908</v>
       </c>
       <c r="B1252" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1253">
@@ -19635,7 +19635,7 @@
         <v>46909</v>
       </c>
       <c r="B1253" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1254">
@@ -19643,7 +19643,7 @@
         <v>46910</v>
       </c>
       <c r="B1254" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1255">
@@ -19651,7 +19651,7 @@
         <v>46911</v>
       </c>
       <c r="B1255" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1256">
@@ -19659,7 +19659,7 @@
         <v>46912</v>
       </c>
       <c r="B1256" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1257">
@@ -19667,7 +19667,7 @@
         <v>46913</v>
       </c>
       <c r="B1257" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1258">
@@ -19675,7 +19675,7 @@
         <v>46914</v>
       </c>
       <c r="B1258" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1259">
@@ -19683,7 +19683,7 @@
         <v>46915</v>
       </c>
       <c r="B1259" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1260">
@@ -19691,7 +19691,7 @@
         <v>46916</v>
       </c>
       <c r="B1260" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1261">
@@ -19699,7 +19699,7 @@
         <v>46917</v>
       </c>
       <c r="B1261" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1262">
@@ -19707,7 +19707,7 @@
         <v>46918</v>
       </c>
       <c r="B1262" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1263">
@@ -19715,7 +19715,7 @@
         <v>46919</v>
       </c>
       <c r="B1263" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1264">
@@ -19723,7 +19723,7 @@
         <v>46920</v>
       </c>
       <c r="B1264" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1265">
@@ -19731,7 +19731,7 @@
         <v>46921</v>
       </c>
       <c r="B1265" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1266">
@@ -19739,7 +19739,7 @@
         <v>46922</v>
       </c>
       <c r="B1266" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1267">
@@ -19747,7 +19747,7 @@
         <v>46923</v>
       </c>
       <c r="B1267" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1268">
@@ -19755,7 +19755,7 @@
         <v>46924</v>
       </c>
       <c r="B1268" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1269">
@@ -19763,7 +19763,7 @@
         <v>46925</v>
       </c>
       <c r="B1269" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1270">
@@ -19771,7 +19771,7 @@
         <v>46926</v>
       </c>
       <c r="B1270" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1271">
@@ -19779,7 +19779,7 @@
         <v>46927</v>
       </c>
       <c r="B1271" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1272">
@@ -19787,7 +19787,7 @@
         <v>46928</v>
       </c>
       <c r="B1272" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1273">
@@ -19795,7 +19795,7 @@
         <v>46929</v>
       </c>
       <c r="B1273" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1274">
@@ -19803,7 +19803,7 @@
         <v>46930</v>
       </c>
       <c r="B1274" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1275">
@@ -19811,7 +19811,7 @@
         <v>46931</v>
       </c>
       <c r="B1275" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1276">
@@ -19819,7 +19819,7 @@
         <v>46932</v>
       </c>
       <c r="B1276" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1277">
@@ -19827,7 +19827,7 @@
         <v>46933</v>
       </c>
       <c r="B1277" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1278">
@@ -19835,7 +19835,7 @@
         <v>46934</v>
       </c>
       <c r="B1278" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1279">
@@ -19843,7 +19843,7 @@
         <v>46935</v>
       </c>
       <c r="B1279" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1280">
@@ -19851,7 +19851,7 @@
         <v>46936</v>
       </c>
       <c r="B1280" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1281">
@@ -19859,7 +19859,7 @@
         <v>46937</v>
       </c>
       <c r="B1281" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1282">
@@ -19867,7 +19867,7 @@
         <v>46938</v>
       </c>
       <c r="B1282" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1283">
@@ -19875,7 +19875,7 @@
         <v>46939</v>
       </c>
       <c r="B1283" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1284">
@@ -19883,7 +19883,7 @@
         <v>46940</v>
       </c>
       <c r="B1284" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1285">
@@ -19891,7 +19891,7 @@
         <v>46941</v>
       </c>
       <c r="B1285" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1286">
@@ -19899,7 +19899,7 @@
         <v>46942</v>
       </c>
       <c r="B1286" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1287">
@@ -19907,7 +19907,7 @@
         <v>46943</v>
       </c>
       <c r="B1287" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1288">
@@ -19915,7 +19915,7 @@
         <v>46944</v>
       </c>
       <c r="B1288" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1289">
@@ -19923,7 +19923,7 @@
         <v>46945</v>
       </c>
       <c r="B1289" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1290">
@@ -19931,7 +19931,7 @@
         <v>46946</v>
       </c>
       <c r="B1290" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1291">
@@ -19939,7 +19939,7 @@
         <v>46947</v>
       </c>
       <c r="B1291" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1292">
@@ -19947,7 +19947,7 @@
         <v>46948</v>
       </c>
       <c r="B1292" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1293">
@@ -19955,7 +19955,7 @@
         <v>46949</v>
       </c>
       <c r="B1293" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1294">
@@ -19963,7 +19963,7 @@
         <v>46950</v>
       </c>
       <c r="B1294" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1295">
@@ -19971,7 +19971,7 @@
         <v>46951</v>
       </c>
       <c r="B1295" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1296">
@@ -19979,7 +19979,7 @@
         <v>46952</v>
       </c>
       <c r="B1296" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1297">
@@ -19987,7 +19987,7 @@
         <v>46953</v>
       </c>
       <c r="B1297" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1298">
@@ -19995,7 +19995,7 @@
         <v>46954</v>
       </c>
       <c r="B1298" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1299">
@@ -20003,7 +20003,7 @@
         <v>46955</v>
       </c>
       <c r="B1299" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1300">
@@ -20011,7 +20011,7 @@
         <v>46956</v>
       </c>
       <c r="B1300" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1301">
@@ -20019,7 +20019,7 @@
         <v>46957</v>
       </c>
       <c r="B1301" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1302">
@@ -20027,7 +20027,7 @@
         <v>46958</v>
       </c>
       <c r="B1302" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1303">
@@ -20035,7 +20035,7 @@
         <v>46959</v>
       </c>
       <c r="B1303" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1304">
@@ -20043,7 +20043,7 @@
         <v>46960</v>
       </c>
       <c r="B1304" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1305">
@@ -20051,7 +20051,7 @@
         <v>46961</v>
       </c>
       <c r="B1305" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1306">
@@ -20059,7 +20059,7 @@
         <v>46962</v>
       </c>
       <c r="B1306" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1307">
@@ -20067,7 +20067,7 @@
         <v>46963</v>
       </c>
       <c r="B1307" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1308">
@@ -20075,7 +20075,7 @@
         <v>46964</v>
       </c>
       <c r="B1308" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1309">
@@ -20083,7 +20083,7 @@
         <v>46965</v>
       </c>
       <c r="B1309" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1310">
@@ -20091,7 +20091,7 @@
         <v>46966</v>
       </c>
       <c r="B1310" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1311">
@@ -20099,7 +20099,7 @@
         <v>46967</v>
       </c>
       <c r="B1311" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1312">
@@ -20107,7 +20107,7 @@
         <v>46968</v>
       </c>
       <c r="B1312" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1313">
@@ -20115,7 +20115,7 @@
         <v>46969</v>
       </c>
       <c r="B1313" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1314">
@@ -20123,7 +20123,7 @@
         <v>46970</v>
       </c>
       <c r="B1314" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1315">
@@ -20131,7 +20131,7 @@
         <v>46971</v>
       </c>
       <c r="B1315" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1316">
@@ -20139,7 +20139,7 @@
         <v>46972</v>
       </c>
       <c r="B1316" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1317">
@@ -20147,7 +20147,7 @@
         <v>46973</v>
       </c>
       <c r="B1317" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1318">
@@ -20155,7 +20155,7 @@
         <v>46974</v>
       </c>
       <c r="B1318" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1319">
@@ -20163,7 +20163,7 @@
         <v>46975</v>
       </c>
       <c r="B1319" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1320">
@@ -20171,7 +20171,7 @@
         <v>46976</v>
       </c>
       <c r="B1320" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1321">
@@ -20179,7 +20179,7 @@
         <v>46977</v>
       </c>
       <c r="B1321" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1322">
@@ -20187,7 +20187,7 @@
         <v>46978</v>
       </c>
       <c r="B1322" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1323">
@@ -20195,7 +20195,7 @@
         <v>46979</v>
       </c>
       <c r="B1323" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1324">
@@ -20203,7 +20203,7 @@
         <v>46980</v>
       </c>
       <c r="B1324" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1325">
@@ -20211,7 +20211,7 @@
         <v>46981</v>
       </c>
       <c r="B1325" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1326">
@@ -20219,7 +20219,7 @@
         <v>46982</v>
       </c>
       <c r="B1326" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1327">
@@ -20227,7 +20227,7 @@
         <v>46983</v>
       </c>
       <c r="B1327" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1328">
@@ -20235,7 +20235,7 @@
         <v>46984</v>
       </c>
       <c r="B1328" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1329">
@@ -20243,7 +20243,7 @@
         <v>46985</v>
       </c>
       <c r="B1329" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1330">
@@ -20251,7 +20251,7 @@
         <v>46986</v>
       </c>
       <c r="B1330" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1331">
@@ -20259,7 +20259,7 @@
         <v>46987</v>
       </c>
       <c r="B1331" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1332">
@@ -20267,7 +20267,7 @@
         <v>46988</v>
       </c>
       <c r="B1332" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1333">
@@ -20275,7 +20275,7 @@
         <v>46989</v>
       </c>
       <c r="B1333" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1334">
@@ -20283,7 +20283,7 @@
         <v>46990</v>
       </c>
       <c r="B1334" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1335">
@@ -20291,7 +20291,7 @@
         <v>46991</v>
       </c>
       <c r="B1335" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1336">
@@ -20299,7 +20299,7 @@
         <v>46992</v>
       </c>
       <c r="B1336" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1337">
@@ -20307,7 +20307,7 @@
         <v>46993</v>
       </c>
       <c r="B1337" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1338">
@@ -20315,7 +20315,7 @@
         <v>46994</v>
       </c>
       <c r="B1338" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1339">
@@ -20323,7 +20323,7 @@
         <v>46995</v>
       </c>
       <c r="B1339" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1340">
@@ -20331,7 +20331,7 @@
         <v>46996</v>
       </c>
       <c r="B1340" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1341">
@@ -20339,7 +20339,7 @@
         <v>46997</v>
       </c>
       <c r="B1341" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1342">
@@ -20347,7 +20347,7 @@
         <v>46998</v>
       </c>
       <c r="B1342" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1343">
@@ -20355,7 +20355,7 @@
         <v>46999</v>
       </c>
       <c r="B1343" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1344">
@@ -20363,7 +20363,7 @@
         <v>47000</v>
       </c>
       <c r="B1344" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1345">
@@ -20371,7 +20371,7 @@
         <v>47001</v>
       </c>
       <c r="B1345" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1346">
@@ -20379,7 +20379,7 @@
         <v>47002</v>
       </c>
       <c r="B1346" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1347">
@@ -20387,7 +20387,7 @@
         <v>47003</v>
       </c>
       <c r="B1347" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1348">
@@ -20395,7 +20395,7 @@
         <v>47004</v>
       </c>
       <c r="B1348" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1349">
@@ -20403,7 +20403,7 @@
         <v>47005</v>
       </c>
       <c r="B1349" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1350">
@@ -20411,7 +20411,7 @@
         <v>47006</v>
       </c>
       <c r="B1350" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1351">
@@ -20419,7 +20419,7 @@
         <v>47007</v>
       </c>
       <c r="B1351" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1352">
@@ -20427,7 +20427,7 @@
         <v>47008</v>
       </c>
       <c r="B1352" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1353">
@@ -20435,7 +20435,7 @@
         <v>47009</v>
       </c>
       <c r="B1353" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1354">
@@ -20443,7 +20443,7 @@
         <v>47010</v>
       </c>
       <c r="B1354" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1355">
@@ -20451,7 +20451,7 @@
         <v>47011</v>
       </c>
       <c r="B1355" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1356">
@@ -20459,7 +20459,7 @@
         <v>47012</v>
       </c>
       <c r="B1356" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1357">
@@ -20467,7 +20467,7 @@
         <v>47013</v>
       </c>
       <c r="B1357" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1358">
@@ -20475,7 +20475,7 @@
         <v>47014</v>
       </c>
       <c r="B1358" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1359">
@@ -20483,7 +20483,7 @@
         <v>47015</v>
       </c>
       <c r="B1359" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1360">
@@ -20491,7 +20491,7 @@
         <v>47016</v>
       </c>
       <c r="B1360" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1361">
@@ -20499,7 +20499,7 @@
         <v>47017</v>
       </c>
       <c r="B1361" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1362">
@@ -20507,7 +20507,7 @@
         <v>47018</v>
       </c>
       <c r="B1362" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1363">
@@ -20515,7 +20515,7 @@
         <v>47019</v>
       </c>
       <c r="B1363" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1364">
@@ -20523,7 +20523,7 @@
         <v>47020</v>
       </c>
       <c r="B1364" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1365">
@@ -20531,7 +20531,7 @@
         <v>47021</v>
       </c>
       <c r="B1365" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1366">
@@ -20539,7 +20539,7 @@
         <v>47022</v>
       </c>
       <c r="B1366" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1367">
@@ -20547,7 +20547,7 @@
         <v>47023</v>
       </c>
       <c r="B1367" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1368">
@@ -20555,7 +20555,7 @@
         <v>47024</v>
       </c>
       <c r="B1368" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1369">
@@ -20563,7 +20563,7 @@
         <v>47025</v>
       </c>
       <c r="B1369" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1370">
@@ -20571,7 +20571,7 @@
         <v>47026</v>
       </c>
       <c r="B1370" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1371">
@@ -20579,7 +20579,7 @@
         <v>47027</v>
       </c>
       <c r="B1371" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1372">
@@ -20587,7 +20587,7 @@
         <v>47028</v>
       </c>
       <c r="B1372" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1373">
@@ -20595,7 +20595,7 @@
         <v>47029</v>
       </c>
       <c r="B1373" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1374">
@@ -20603,7 +20603,7 @@
         <v>47030</v>
       </c>
       <c r="B1374" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1375">
@@ -20611,7 +20611,7 @@
         <v>47031</v>
       </c>
       <c r="B1375" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1376">
@@ -20619,7 +20619,7 @@
         <v>47032</v>
       </c>
       <c r="B1376" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1377">
@@ -20627,7 +20627,7 @@
         <v>47033</v>
       </c>
       <c r="B1377" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1378">
@@ -20635,7 +20635,7 @@
         <v>47034</v>
       </c>
       <c r="B1378" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1379">
@@ -20643,7 +20643,7 @@
         <v>47035</v>
       </c>
       <c r="B1379" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1380">
@@ -20651,7 +20651,7 @@
         <v>47036</v>
       </c>
       <c r="B1380" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1381">
@@ -20659,7 +20659,7 @@
         <v>47037</v>
       </c>
       <c r="B1381" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1382">
@@ -20667,7 +20667,7 @@
         <v>47038</v>
       </c>
       <c r="B1382" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1383">
@@ -20675,7 +20675,7 @@
         <v>47039</v>
       </c>
       <c r="B1383" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1384">
@@ -20683,7 +20683,7 @@
         <v>47040</v>
       </c>
       <c r="B1384" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1385">
@@ -20691,7 +20691,7 @@
         <v>47041</v>
       </c>
       <c r="B1385" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1386">
@@ -20699,7 +20699,7 @@
         <v>47042</v>
       </c>
       <c r="B1386" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1387">
@@ -20707,7 +20707,7 @@
         <v>47043</v>
       </c>
       <c r="B1387" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1388">
@@ -20715,7 +20715,7 @@
         <v>47044</v>
       </c>
       <c r="B1388" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1389">
@@ -20723,7 +20723,7 @@
         <v>47045</v>
       </c>
       <c r="B1389" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1390">
@@ -20731,7 +20731,7 @@
         <v>47046</v>
       </c>
       <c r="B1390" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1391">
@@ -20739,7 +20739,7 @@
         <v>47047</v>
       </c>
       <c r="B1391" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1392">
@@ -20747,7 +20747,7 @@
         <v>47048</v>
       </c>
       <c r="B1392" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1393">
@@ -20755,7 +20755,7 @@
         <v>47049</v>
       </c>
       <c r="B1393" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1394">
@@ -20763,7 +20763,7 @@
         <v>47050</v>
       </c>
       <c r="B1394" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1395">
@@ -20771,7 +20771,7 @@
         <v>47051</v>
       </c>
       <c r="B1395" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1396">
@@ -20779,7 +20779,7 @@
         <v>47052</v>
       </c>
       <c r="B1396" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1397">
@@ -20787,7 +20787,7 @@
         <v>47053</v>
       </c>
       <c r="B1397" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1398">
@@ -20795,7 +20795,7 @@
         <v>47054</v>
       </c>
       <c r="B1398" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1399">
@@ -20803,7 +20803,7 @@
         <v>47055</v>
       </c>
       <c r="B1399" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1400">
@@ -20811,7 +20811,7 @@
         <v>47056</v>
       </c>
       <c r="B1400" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1401">
@@ -20819,7 +20819,7 @@
         <v>47057</v>
       </c>
       <c r="B1401" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1402">
@@ -20827,7 +20827,7 @@
         <v>47058</v>
       </c>
       <c r="B1402" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1403">
@@ -20835,7 +20835,7 @@
         <v>47059</v>
       </c>
       <c r="B1403" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1404">
@@ -20843,7 +20843,7 @@
         <v>47060</v>
       </c>
       <c r="B1404" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1405">
@@ -20851,7 +20851,7 @@
         <v>47061</v>
       </c>
       <c r="B1405" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1406">
@@ -20859,7 +20859,7 @@
         <v>47062</v>
       </c>
       <c r="B1406" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1407">
@@ -20867,7 +20867,7 @@
         <v>47063</v>
       </c>
       <c r="B1407" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1408">
@@ -20875,7 +20875,7 @@
         <v>47064</v>
       </c>
       <c r="B1408" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1409">
@@ -20883,7 +20883,7 @@
         <v>47065</v>
       </c>
       <c r="B1409" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1410">
@@ -20891,7 +20891,7 @@
         <v>47066</v>
       </c>
       <c r="B1410" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1411">
@@ -20899,7 +20899,7 @@
         <v>47067</v>
       </c>
       <c r="B1411" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1412">
@@ -20907,7 +20907,7 @@
         <v>47068</v>
       </c>
       <c r="B1412" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1413">
@@ -20915,7 +20915,7 @@
         <v>47069</v>
       </c>
       <c r="B1413" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1414">
@@ -20923,7 +20923,7 @@
         <v>47070</v>
       </c>
       <c r="B1414" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1415">
@@ -20931,7 +20931,7 @@
         <v>47071</v>
       </c>
       <c r="B1415" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1416">
@@ -20939,7 +20939,7 @@
         <v>47072</v>
       </c>
       <c r="B1416" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1417">
@@ -20947,7 +20947,7 @@
         <v>47073</v>
       </c>
       <c r="B1417" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1418">
@@ -20955,7 +20955,7 @@
         <v>47074</v>
       </c>
       <c r="B1418" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1419">
@@ -20963,7 +20963,7 @@
         <v>47075</v>
       </c>
       <c r="B1419" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1420">
@@ -20971,7 +20971,7 @@
         <v>47076</v>
       </c>
       <c r="B1420" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1421">
@@ -20979,7 +20979,7 @@
         <v>47077</v>
       </c>
       <c r="B1421" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1422">
@@ -20987,7 +20987,7 @@
         <v>47078</v>
       </c>
       <c r="B1422" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1423">
@@ -20995,7 +20995,7 @@
         <v>47079</v>
       </c>
       <c r="B1423" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1424">
@@ -21003,7 +21003,7 @@
         <v>47080</v>
       </c>
       <c r="B1424" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1425">
@@ -21011,7 +21011,7 @@
         <v>47081</v>
       </c>
       <c r="B1425" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1426">
@@ -21019,7 +21019,7 @@
         <v>47082</v>
       </c>
       <c r="B1426" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1427">
@@ -21027,7 +21027,7 @@
         <v>47083</v>
       </c>
       <c r="B1427" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1428">
@@ -21035,7 +21035,7 @@
         <v>47084</v>
       </c>
       <c r="B1428" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1429">
@@ -21043,7 +21043,7 @@
         <v>47085</v>
       </c>
       <c r="B1429" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1430">
@@ -21051,7 +21051,7 @@
         <v>47086</v>
       </c>
       <c r="B1430" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1431">
@@ -21059,7 +21059,7 @@
         <v>47087</v>
       </c>
       <c r="B1431" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1432">
@@ -21067,7 +21067,7 @@
         <v>47088</v>
       </c>
       <c r="B1432" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1433">
@@ -21075,7 +21075,7 @@
         <v>47089</v>
       </c>
       <c r="B1433" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1434">
@@ -21083,7 +21083,7 @@
         <v>47090</v>
       </c>
       <c r="B1434" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1435">
@@ -21091,7 +21091,7 @@
         <v>47091</v>
       </c>
       <c r="B1435" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1436">
@@ -21099,7 +21099,7 @@
         <v>47092</v>
       </c>
       <c r="B1436" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1437">
@@ -21107,7 +21107,7 @@
         <v>47093</v>
       </c>
       <c r="B1437" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1438">
@@ -21115,7 +21115,7 @@
         <v>47094</v>
       </c>
       <c r="B1438" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1439">
@@ -21123,7 +21123,7 @@
         <v>47095</v>
       </c>
       <c r="B1439" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1440">
@@ -21131,7 +21131,7 @@
         <v>47096</v>
       </c>
       <c r="B1440" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1441">
@@ -21139,7 +21139,7 @@
         <v>47097</v>
       </c>
       <c r="B1441" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1442">
@@ -21147,7 +21147,7 @@
         <v>47098</v>
       </c>
       <c r="B1442" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1443">
@@ -21155,7 +21155,7 @@
         <v>47099</v>
       </c>
       <c r="B1443" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1444">
@@ -21163,7 +21163,7 @@
         <v>47100</v>
       </c>
       <c r="B1444" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1445">
@@ -21171,7 +21171,7 @@
         <v>47101</v>
       </c>
       <c r="B1445" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1446">
@@ -21179,7 +21179,7 @@
         <v>47102</v>
       </c>
       <c r="B1446" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1447">
@@ -21187,7 +21187,7 @@
         <v>47103</v>
       </c>
       <c r="B1447" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1448">
@@ -21195,7 +21195,7 @@
         <v>47104</v>
       </c>
       <c r="B1448" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1449">
@@ -21203,7 +21203,7 @@
         <v>47105</v>
       </c>
       <c r="B1449" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1450">
@@ -21211,7 +21211,7 @@
         <v>47106</v>
       </c>
       <c r="B1450" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1451">
@@ -21219,7 +21219,7 @@
         <v>47107</v>
       </c>
       <c r="B1451" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1452">
@@ -21227,7 +21227,7 @@
         <v>47108</v>
       </c>
       <c r="B1452" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1453">
@@ -21235,7 +21235,7 @@
         <v>47109</v>
       </c>
       <c r="B1453" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1454">
@@ -21243,7 +21243,7 @@
         <v>47110</v>
       </c>
       <c r="B1454" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1455">
@@ -21251,7 +21251,7 @@
         <v>47111</v>
       </c>
       <c r="B1455" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1456">
@@ -21259,7 +21259,7 @@
         <v>47112</v>
       </c>
       <c r="B1456" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1457">
@@ -21267,7 +21267,7 @@
         <v>47113</v>
       </c>
       <c r="B1457" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1458">
@@ -21275,7 +21275,7 @@
         <v>47114</v>
       </c>
       <c r="B1458" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1459">
@@ -21283,7 +21283,7 @@
         <v>47115</v>
       </c>
       <c r="B1459" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1460">
@@ -21291,7 +21291,7 @@
         <v>47116</v>
       </c>
       <c r="B1460" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1461">
@@ -21299,7 +21299,7 @@
         <v>47117</v>
       </c>
       <c r="B1461" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="1462">
@@ -21307,7 +21307,7 @@
         <v>47118</v>
       </c>
       <c r="B1462" t="n">
-        <v>26.37</v>
+        <v>26.7</v>
       </c>
     </row>
   </sheetData>
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
     </row>
   </sheetData>

--- a/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
+++ b/Tarifarios_🔥_Gas_Natural_Tiago_Felicia.xlsx
@@ -13163,7 +13163,7 @@
         <v>46100</v>
       </c>
       <c r="B444" t="n">
-        <v>50.75</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="445">
@@ -13171,7 +13171,7 @@
         <v>46101</v>
       </c>
       <c r="B445" t="n">
-        <v>50.75</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="446">
@@ -13179,7 +13179,7 @@
         <v>46102</v>
       </c>
       <c r="B446" t="n">
-        <v>51.25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="447">
@@ -13187,7 +13187,7 @@
         <v>46103</v>
       </c>
       <c r="B447" t="n">
-        <v>51.25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="448">
@@ -13195,7 +13195,7 @@
         <v>46104</v>
       </c>
       <c r="B448" t="n">
-        <v>50.92</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="449">
@@ -13203,7 +13203,7 @@
         <v>46105</v>
       </c>
       <c r="B449" t="n">
-        <v>50.92</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="450">
@@ -13211,7 +13211,7 @@
         <v>46106</v>
       </c>
       <c r="B450" t="n">
-        <v>50.92</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="451">
@@ -13219,7 +13219,7 @@
         <v>46107</v>
       </c>
       <c r="B451" t="n">
-        <v>50.92</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="452">
@@ -13227,7 +13227,7 @@
         <v>46108</v>
       </c>
       <c r="B452" t="n">
-        <v>50.92</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="453">
@@ -13235,7 +13235,7 @@
         <v>46109</v>
       </c>
       <c r="B453" t="n">
-        <v>50.92</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="454">
@@ -13243,7 +13243,7 @@
         <v>46110</v>
       </c>
       <c r="B454" t="n">
-        <v>50.92</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="455">
@@ -13251,7 +13251,7 @@
         <v>46111</v>
       </c>
       <c r="B455" t="n">
-        <v>50.89</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="456">
@@ -13259,7 +13259,7 @@
         <v>46112</v>
       </c>
       <c r="B456" t="n">
-        <v>50.89</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="457">
@@ -13267,7 +13267,7 @@
         <v>46113</v>
       </c>
       <c r="B457" t="n">
-        <v>50.89</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="458">
@@ -13275,7 +13275,7 @@
         <v>46114</v>
       </c>
       <c r="B458" t="n">
-        <v>50.89</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="459">
@@ -13283,7 +13283,7 @@
         <v>46115</v>
       </c>
       <c r="B459" t="n">
-        <v>50.89</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="460">
@@ -13291,7 +13291,7 @@
         <v>46116</v>
       </c>
       <c r="B460" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="461">
@@ -13299,7 +13299,7 @@
         <v>46117</v>
       </c>
       <c r="B461" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="462">
@@ -13307,7 +13307,7 @@
         <v>46118</v>
       </c>
       <c r="B462" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="463">
@@ -13315,7 +13315,7 @@
         <v>46119</v>
       </c>
       <c r="B463" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="464">
@@ -13323,7 +13323,7 @@
         <v>46120</v>
       </c>
       <c r="B464" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="465">
@@ -13331,7 +13331,7 @@
         <v>46121</v>
       </c>
       <c r="B465" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="466">
@@ -13339,7 +13339,7 @@
         <v>46122</v>
       </c>
       <c r="B466" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="467">
@@ -13347,7 +13347,7 @@
         <v>46123</v>
       </c>
       <c r="B467" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="468">
@@ -13355,7 +13355,7 @@
         <v>46124</v>
       </c>
       <c r="B468" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="469">
@@ -13363,7 +13363,7 @@
         <v>46125</v>
       </c>
       <c r="B469" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="470">
@@ -13371,7 +13371,7 @@
         <v>46126</v>
       </c>
       <c r="B470" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="471">
@@ -13379,7 +13379,7 @@
         <v>46127</v>
       </c>
       <c r="B471" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="472">
@@ -13387,7 +13387,7 @@
         <v>46128</v>
       </c>
       <c r="B472" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="473">
@@ -13395,7 +13395,7 @@
         <v>46129</v>
       </c>
       <c r="B473" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="474">
@@ -13403,7 +13403,7 @@
         <v>46130</v>
       </c>
       <c r="B474" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="475">
@@ -13411,7 +13411,7 @@
         <v>46131</v>
       </c>
       <c r="B475" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="476">
@@ -13419,7 +13419,7 @@
         <v>46132</v>
       </c>
       <c r="B476" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="477">
@@ -13427,7 +13427,7 @@
         <v>46133</v>
       </c>
       <c r="B477" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="478">
@@ -13435,7 +13435,7 @@
         <v>46134</v>
       </c>
       <c r="B478" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="479">
@@ -13443,7 +13443,7 @@
         <v>46135</v>
       </c>
       <c r="B479" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="480">
@@ -13451,7 +13451,7 @@
         <v>46136</v>
       </c>
       <c r="B480" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="481">
@@ -13459,7 +13459,7 @@
         <v>46137</v>
       </c>
       <c r="B481" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="482">
@@ -13467,7 +13467,7 @@
         <v>46138</v>
       </c>
       <c r="B482" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="483">
@@ -13475,7 +13475,7 @@
         <v>46139</v>
       </c>
       <c r="B483" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="484">
@@ -13483,7 +13483,7 @@
         <v>46140</v>
       </c>
       <c r="B484" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="485">
@@ -13491,7 +13491,7 @@
         <v>46141</v>
       </c>
       <c r="B485" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="486">
@@ -13499,7 +13499,7 @@
         <v>46142</v>
       </c>
       <c r="B486" t="n">
-        <v>50.87</v>
+        <v>54.01</v>
       </c>
     </row>
     <row r="487">
@@ -13507,7 +13507,7 @@
         <v>46143</v>
       </c>
       <c r="B487" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="488">
@@ -13515,7 +13515,7 @@
         <v>46144</v>
       </c>
       <c r="B488" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="489">
@@ -13523,7 +13523,7 @@
         <v>46145</v>
       </c>
       <c r="B489" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="490">
@@ -13531,7 +13531,7 @@
         <v>46146</v>
       </c>
       <c r="B490" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="491">
@@ -13539,7 +13539,7 @@
         <v>46147</v>
       </c>
       <c r="B491" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="492">
@@ -13547,7 +13547,7 @@
         <v>46148</v>
       </c>
       <c r="B492" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="493">
@@ -13555,7 +13555,7 @@
         <v>46149</v>
       </c>
       <c r="B493" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="494">
@@ -13563,7 +13563,7 @@
         <v>46150</v>
       </c>
       <c r="B494" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="495">
@@ -13571,7 +13571,7 @@
         <v>46151</v>
       </c>
       <c r="B495" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="496">
@@ -13579,7 +13579,7 @@
         <v>46152</v>
       </c>
       <c r="B496" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="497">
@@ -13587,7 +13587,7 @@
         <v>46153</v>
       </c>
       <c r="B497" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="498">
@@ -13595,7 +13595,7 @@
         <v>46154</v>
       </c>
       <c r="B498" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="499">
@@ -13603,7 +13603,7 @@
         <v>46155</v>
       </c>
       <c r="B499" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="500">
@@ -13611,7 +13611,7 @@
         <v>46156</v>
       </c>
       <c r="B500" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="501">
@@ -13619,7 +13619,7 @@
         <v>46157</v>
       </c>
       <c r="B501" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="502">
@@ -13627,7 +13627,7 @@
         <v>46158</v>
       </c>
       <c r="B502" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="503">
@@ -13635,7 +13635,7 @@
         <v>46159</v>
       </c>
       <c r="B503" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="504">
@@ -13643,7 +13643,7 @@
         <v>46160</v>
       </c>
       <c r="B504" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="505">
@@ -13651,7 +13651,7 @@
         <v>46161</v>
       </c>
       <c r="B505" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="506">
@@ -13659,7 +13659,7 @@
         <v>46162</v>
       </c>
       <c r="B506" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="507">
@@ -13667,7 +13667,7 @@
         <v>46163</v>
       </c>
       <c r="B507" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="508">
@@ -13675,7 +13675,7 @@
         <v>46164</v>
       </c>
       <c r="B508" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="509">
@@ -13683,7 +13683,7 @@
         <v>46165</v>
       </c>
       <c r="B509" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="510">
@@ -13691,7 +13691,7 @@
         <v>46166</v>
       </c>
       <c r="B510" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="511">
@@ -13699,7 +13699,7 @@
         <v>46167</v>
       </c>
       <c r="B511" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="512">
@@ -13707,7 +13707,7 @@
         <v>46168</v>
       </c>
       <c r="B512" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="513">
@@ -13715,7 +13715,7 @@
         <v>46169</v>
       </c>
       <c r="B513" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="514">
@@ -13723,7 +13723,7 @@
         <v>46170</v>
       </c>
       <c r="B514" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="515">
@@ -13731,7 +13731,7 @@
         <v>46171</v>
       </c>
       <c r="B515" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="516">
@@ -13739,7 +13739,7 @@
         <v>46172</v>
       </c>
       <c r="B516" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="517">
@@ -13747,7 +13747,7 @@
         <v>46173</v>
       </c>
       <c r="B517" t="n">
-        <v>50.85</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="518">
@@ -13755,7 +13755,7 @@
         <v>46174</v>
       </c>
       <c r="B518" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="519">
@@ -13763,7 +13763,7 @@
         <v>46175</v>
       </c>
       <c r="B519" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="520">
@@ -13771,7 +13771,7 @@
         <v>46176</v>
       </c>
       <c r="B520" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="521">
@@ -13779,7 +13779,7 @@
         <v>46177</v>
       </c>
       <c r="B521" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="522">
@@ -13787,7 +13787,7 @@
         <v>46178</v>
       </c>
       <c r="B522" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="523">
@@ -13795,7 +13795,7 @@
         <v>46179</v>
       </c>
       <c r="B523" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="524">
@@ -13803,7 +13803,7 @@
         <v>46180</v>
       </c>
       <c r="B524" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="525">
@@ -13811,7 +13811,7 @@
         <v>46181</v>
       </c>
       <c r="B525" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="526">
@@ -13819,7 +13819,7 @@
         <v>46182</v>
       </c>
       <c r="B526" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="527">
@@ -13827,7 +13827,7 @@
         <v>46183</v>
       </c>
       <c r="B527" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="528">
@@ -13835,7 +13835,7 @@
         <v>46184</v>
       </c>
       <c r="B528" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="529">
@@ -13843,7 +13843,7 @@
         <v>46185</v>
       </c>
       <c r="B529" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="530">
@@ -13851,7 +13851,7 @@
         <v>46186</v>
       </c>
       <c r="B530" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="531">
@@ -13859,7 +13859,7 @@
         <v>46187</v>
       </c>
       <c r="B531" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="532">
@@ -13867,7 +13867,7 @@
         <v>46188</v>
       </c>
       <c r="B532" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="533">
@@ -13875,7 +13875,7 @@
         <v>46189</v>
       </c>
       <c r="B533" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="534">
@@ -13883,7 +13883,7 @@
         <v>46190</v>
       </c>
       <c r="B534" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="535">
@@ -13891,7 +13891,7 @@
         <v>46191</v>
       </c>
       <c r="B535" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="536">
@@ -13899,7 +13899,7 @@
         <v>46192</v>
       </c>
       <c r="B536" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="537">
@@ -13907,7 +13907,7 @@
         <v>46193</v>
       </c>
       <c r="B537" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="538">
@@ -13915,7 +13915,7 @@
         <v>46194</v>
       </c>
       <c r="B538" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="539">
@@ -13923,7 +13923,7 @@
         <v>46195</v>
       </c>
       <c r="B539" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="540">
@@ -13931,7 +13931,7 @@
         <v>46196</v>
       </c>
       <c r="B540" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="541">
@@ -13939,7 +13939,7 @@
         <v>46197</v>
       </c>
       <c r="B541" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="542">
@@ -13947,7 +13947,7 @@
         <v>46198</v>
       </c>
       <c r="B542" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="543">
@@ -13955,7 +13955,7 @@
         <v>46199</v>
       </c>
       <c r="B543" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="544">
@@ -13963,7 +13963,7 @@
         <v>46200</v>
       </c>
       <c r="B544" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="545">
@@ -13971,7 +13971,7 @@
         <v>46201</v>
       </c>
       <c r="B545" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="546">
@@ -13979,7 +13979,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="547">
@@ -13987,7 +13987,7 @@
         <v>46203</v>
       </c>
       <c r="B547" t="n">
-        <v>50.49</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="548">
@@ -13995,7 +13995,7 @@
         <v>46204</v>
       </c>
       <c r="B548" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="549">
@@ -14003,7 +14003,7 @@
         <v>46205</v>
       </c>
       <c r="B549" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="550">
@@ -14011,7 +14011,7 @@
         <v>46206</v>
       </c>
       <c r="B550" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="551">
@@ -14019,7 +14019,7 @@
         <v>46207</v>
       </c>
       <c r="B551" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="552">
@@ -14027,7 +14027,7 @@
         <v>46208</v>
       </c>
       <c r="B552" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="553">
@@ -14035,7 +14035,7 @@
         <v>46209</v>
       </c>
       <c r="B553" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="554">
@@ -14043,7 +14043,7 @@
         <v>46210</v>
       </c>
       <c r="B554" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="555">
@@ -14051,7 +14051,7 @@
         <v>46211</v>
       </c>
       <c r="B555" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="556">
@@ -14059,7 +14059,7 @@
         <v>46212</v>
       </c>
       <c r="B556" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="557">
@@ -14067,7 +14067,7 @@
         <v>46213</v>
       </c>
       <c r="B557" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="558">
@@ -14075,7 +14075,7 @@
         <v>46214</v>
       </c>
       <c r="B558" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="559">
@@ -14083,7 +14083,7 @@
         <v>46215</v>
       </c>
       <c r="B559" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="560">
@@ -14091,7 +14091,7 @@
         <v>46216</v>
       </c>
       <c r="B560" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="561">
@@ -14099,7 +14099,7 @@
         <v>46217</v>
       </c>
       <c r="B561" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="562">
@@ -14107,7 +14107,7 @@
         <v>46218</v>
       </c>
       <c r="B562" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="563">
@@ -14115,7 +14115,7 @@
         <v>46219</v>
       </c>
       <c r="B563" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="564">
@@ -14123,7 +14123,7 @@
         <v>46220</v>
       </c>
       <c r="B564" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="565">
@@ -14131,7 +14131,7 @@
         <v>46221</v>
       </c>
       <c r="B565" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="566">
@@ -14139,7 +14139,7 @@
         <v>46222</v>
       </c>
       <c r="B566" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="567">
@@ -14147,7 +14147,7 @@
         <v>46223</v>
       </c>
       <c r="B567" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="568">
@@ -14155,7 +14155,7 @@
         <v>46224</v>
       </c>
       <c r="B568" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="569">
@@ -14163,7 +14163,7 @@
         <v>46225</v>
       </c>
       <c r="B569" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="570">
@@ -14171,7 +14171,7 @@
         <v>46226</v>
       </c>
       <c r="B570" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="571">
@@ -14179,7 +14179,7 @@
         <v>46227</v>
       </c>
       <c r="B571" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="572">
@@ -14187,7 +14187,7 @@
         <v>46228</v>
       </c>
       <c r="B572" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="573">
@@ -14195,7 +14195,7 @@
         <v>46229</v>
       </c>
       <c r="B573" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="574">
@@ -14203,7 +14203,7 @@
         <v>46230</v>
       </c>
       <c r="B574" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="575">
@@ -14211,7 +14211,7 @@
         <v>46231</v>
       </c>
       <c r="B575" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="576">
@@ -14219,7 +14219,7 @@
         <v>46232</v>
       </c>
       <c r="B576" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="577">
@@ -14227,7 +14227,7 @@
         <v>46233</v>
       </c>
       <c r="B577" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="578">
@@ -14235,7 +14235,7 @@
         <v>46234</v>
       </c>
       <c r="B578" t="n">
-        <v>50.26</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="579">
@@ -14243,7 +14243,7 @@
         <v>46235</v>
       </c>
       <c r="B579" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="580">
@@ -14251,7 +14251,7 @@
         <v>46236</v>
       </c>
       <c r="B580" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="581">
@@ -14259,7 +14259,7 @@
         <v>46237</v>
       </c>
       <c r="B581" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="582">
@@ -14267,7 +14267,7 @@
         <v>46238</v>
       </c>
       <c r="B582" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="583">
@@ -14275,7 +14275,7 @@
         <v>46239</v>
       </c>
       <c r="B583" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="584">
@@ -14283,7 +14283,7 @@
         <v>46240</v>
       </c>
       <c r="B584" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="585">
@@ -14291,7 +14291,7 @@
         <v>46241</v>
       </c>
       <c r="B585" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="586">
@@ -14299,7 +14299,7 @@
         <v>46242</v>
       </c>
       <c r="B586" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="587">
@@ -14307,7 +14307,7 @@
         <v>46243</v>
       </c>
       <c r="B587" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="588">
@@ -14315,7 +14315,7 @@
         <v>46244</v>
       </c>
       <c r="B588" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="589">
@@ -14323,7 +14323,7 @@
         <v>46245</v>
       </c>
       <c r="B589" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="590">
@@ -14331,7 +14331,7 @@
         <v>46246</v>
       </c>
       <c r="B590" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="591">
@@ -14339,7 +14339,7 @@
         <v>46247</v>
       </c>
       <c r="B591" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="592">
@@ -14347,7 +14347,7 @@
         <v>46248</v>
       </c>
       <c r="B592" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="593">
@@ -14355,7 +14355,7 @@
         <v>46249</v>
       </c>
       <c r="B593" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="594">
@@ -14363,7 +14363,7 @@
         <v>46250</v>
       </c>
       <c r="B594" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="595">
@@ -14371,7 +14371,7 @@
         <v>46251</v>
       </c>
       <c r="B595" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="596">
@@ -14379,7 +14379,7 @@
         <v>46252</v>
       </c>
       <c r="B596" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="597">
@@ -14387,7 +14387,7 @@
         <v>46253</v>
       </c>
       <c r="B597" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="598">
@@ -14395,7 +14395,7 @@
         <v>46254</v>
       </c>
       <c r="B598" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="599">
@@ -14403,7 +14403,7 @@
         <v>46255</v>
       </c>
       <c r="B599" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="600">
@@ -14411,7 +14411,7 @@
         <v>46256</v>
       </c>
       <c r="B600" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="601">
@@ -14419,7 +14419,7 @@
         <v>46257</v>
       </c>
       <c r="B601" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="602">
@@ -14427,7 +14427,7 @@
         <v>46258</v>
       </c>
       <c r="B602" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="603">
@@ -14435,7 +14435,7 @@
         <v>46259</v>
       </c>
       <c r="B603" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="604">
@@ -14443,7 +14443,7 @@
         <v>46260</v>
       </c>
       <c r="B604" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="605">
@@ -14451,7 +14451,7 @@
         <v>46261</v>
       </c>
       <c r="B605" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="606">
@@ -14459,7 +14459,7 @@
         <v>46262</v>
       </c>
       <c r="B606" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="607">
@@ -14467,7 +14467,7 @@
         <v>46263</v>
       </c>
       <c r="B607" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="608">
@@ -14475,7 +14475,7 @@
         <v>46264</v>
       </c>
       <c r="B608" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="609">
@@ -14483,7 +14483,7 @@
         <v>46265</v>
       </c>
       <c r="B609" t="n">
-        <v>50.02</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="610">
@@ -14491,7 +14491,7 @@
         <v>46266</v>
       </c>
       <c r="B610" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="611">
@@ -14499,7 +14499,7 @@
         <v>46267</v>
       </c>
       <c r="B611" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="612">
@@ -14507,7 +14507,7 @@
         <v>46268</v>
       </c>
       <c r="B612" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="613">
@@ -14515,7 +14515,7 @@
         <v>46269</v>
       </c>
       <c r="B613" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="614">
@@ -14523,7 +14523,7 @@
         <v>46270</v>
       </c>
       <c r="B614" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="615">
@@ -14531,7 +14531,7 @@
         <v>46271</v>
       </c>
       <c r="B615" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="616">
@@ -14539,7 +14539,7 @@
         <v>46272</v>
       </c>
       <c r="B616" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="617">
@@ -14547,7 +14547,7 @@
         <v>46273</v>
       </c>
       <c r="B617" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="618">
@@ -14555,7 +14555,7 @@
         <v>46274</v>
       </c>
       <c r="B618" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="619">
@@ -14563,7 +14563,7 @@
         <v>46275</v>
       </c>
       <c r="B619" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="620">
@@ -14571,7 +14571,7 @@
         <v>46276</v>
       </c>
       <c r="B620" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="621">
@@ -14579,7 +14579,7 @@
         <v>46277</v>
       </c>
       <c r="B621" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="622">
@@ -14587,7 +14587,7 @@
         <v>46278</v>
       </c>
       <c r="B622" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="623">
@@ -14595,7 +14595,7 @@
         <v>46279</v>
       </c>
       <c r="B623" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="624">
@@ -14603,7 +14603,7 @@
         <v>46280</v>
       </c>
       <c r="B624" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="625">
@@ -14611,7 +14611,7 @@
         <v>46281</v>
       </c>
       <c r="B625" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="626">
@@ -14619,7 +14619,7 @@
         <v>46282</v>
       </c>
       <c r="B626" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="627">
@@ -14627,7 +14627,7 @@
         <v>46283</v>
       </c>
       <c r="B627" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="628">
@@ -14635,7 +14635,7 @@
         <v>46284</v>
       </c>
       <c r="B628" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="629">
@@ -14643,7 +14643,7 @@
         <v>46285</v>
       </c>
       <c r="B629" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="630">
@@ -14651,7 +14651,7 @@
         <v>46286</v>
       </c>
       <c r="B630" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="631">
@@ -14659,7 +14659,7 @@
         <v>46287</v>
       </c>
       <c r="B631" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="632">
@@ -14667,7 +14667,7 @@
         <v>46288</v>
       </c>
       <c r="B632" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="633">
@@ -14675,7 +14675,7 @@
         <v>46289</v>
       </c>
       <c r="B633" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="634">
@@ -14683,7 +14683,7 @@
         <v>46290</v>
       </c>
       <c r="B634" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="635">
@@ -14691,7 +14691,7 @@
         <v>46291</v>
       </c>
       <c r="B635" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="636">
@@ -14699,7 +14699,7 @@
         <v>46292</v>
       </c>
       <c r="B636" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="637">
@@ -14707,7 +14707,7 @@
         <v>46293</v>
       </c>
       <c r="B637" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="638">
@@ -14715,7 +14715,7 @@
         <v>46294</v>
       </c>
       <c r="B638" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="639">
@@ -14723,7 +14723,7 @@
         <v>46295</v>
       </c>
       <c r="B639" t="n">
-        <v>49.87</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="640">
@@ -14731,7 +14731,7 @@
         <v>46296</v>
       </c>
       <c r="B640" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="641">
@@ -14739,7 +14739,7 @@
         <v>46297</v>
       </c>
       <c r="B641" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="642">
@@ -14747,7 +14747,7 @@
         <v>46298</v>
       </c>
       <c r="B642" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="643">
@@ -14755,7 +14755,7 @@
         <v>46299</v>
       </c>
       <c r="B643" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="644">
@@ -14763,7 +14763,7 @@
         <v>46300</v>
       </c>
       <c r="B644" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="645">
@@ -14771,7 +14771,7 @@
         <v>46301</v>
       </c>
       <c r="B645" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="646">
@@ -14779,7 +14779,7 @@
         <v>46302</v>
       </c>
       <c r="B646" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="647">
@@ -14787,7 +14787,7 @@
         <v>46303</v>
       </c>
       <c r="B647" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="648">
@@ -14795,7 +14795,7 @@
         <v>46304</v>
       </c>
       <c r="B648" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="649">
@@ -14803,7 +14803,7 @@
         <v>46305</v>
       </c>
       <c r="B649" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="650">
@@ -14811,7 +14811,7 @@
         <v>46306</v>
       </c>
       <c r="B650" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="651">
@@ -14819,7 +14819,7 @@
         <v>46307</v>
       </c>
       <c r="B651" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="652">
@@ -14827,7 +14827,7 @@
         <v>46308</v>
       </c>
       <c r="B652" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="653">
@@ -14835,7 +14835,7 @@
         <v>46309</v>
       </c>
       <c r="B653" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="654">
@@ -14843,7 +14843,7 @@
         <v>46310</v>
       </c>
       <c r="B654" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="655">
@@ -14851,7 +14851,7 @@
         <v>46311</v>
       </c>
       <c r="B655" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="656">
@@ -14859,7 +14859,7 @@
         <v>46312</v>
       </c>
       <c r="B656" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="657">
@@ -14867,7 +14867,7 @@
         <v>46313</v>
       </c>
       <c r="B657" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="658">
@@ -14875,7 +14875,7 @@
         <v>46314</v>
       </c>
       <c r="B658" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="659">
@@ -14883,7 +14883,7 @@
         <v>46315</v>
       </c>
       <c r="B659" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="660">
@@ -14891,7 +14891,7 @@
         <v>46316</v>
       </c>
       <c r="B660" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="661">
@@ -14899,7 +14899,7 @@
         <v>46317</v>
       </c>
       <c r="B661" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="662">
@@ -14907,7 +14907,7 @@
         <v>46318</v>
       </c>
       <c r="B662" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="663">
@@ -14915,7 +14915,7 @@
         <v>46319</v>
       </c>
       <c r="B663" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="664">
@@ -14923,7 +14923,7 @@
         <v>46320</v>
       </c>
       <c r="B664" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="665">
@@ -14931,7 +14931,7 @@
         <v>46321</v>
       </c>
       <c r="B665" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="666">
@@ -14939,7 +14939,7 @@
         <v>46322</v>
       </c>
       <c r="B666" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="667">
@@ -14947,7 +14947,7 @@
         <v>46323</v>
       </c>
       <c r="B667" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="668">
@@ -14955,7 +14955,7 @@
         <v>46324</v>
       </c>
       <c r="B668" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="669">
@@ -14963,7 +14963,7 @@
         <v>46325</v>
       </c>
       <c r="B669" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="670">
@@ -14971,7 +14971,7 @@
         <v>46326</v>
       </c>
       <c r="B670" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="671">
@@ -14979,7 +14979,7 @@
         <v>46327</v>
       </c>
       <c r="B671" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="672">
@@ -14987,7 +14987,7 @@
         <v>46328</v>
       </c>
       <c r="B672" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="673">
@@ -14995,7 +14995,7 @@
         <v>46329</v>
       </c>
       <c r="B673" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="674">
@@ -15003,7 +15003,7 @@
         <v>46330</v>
       </c>
       <c r="B674" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="675">
@@ -15011,7 +15011,7 @@
         <v>46331</v>
       </c>
       <c r="B675" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="676">
@@ -15019,7 +15019,7 @@
         <v>46332</v>
       </c>
       <c r="B676" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="677">
@@ -15027,7 +15027,7 @@
         <v>46333</v>
       </c>
       <c r="B677" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="678">
@@ -15035,7 +15035,7 @@
         <v>46334</v>
       </c>
       <c r="B678" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="679">
@@ -15043,7 +15043,7 @@
         <v>46335</v>
       </c>
       <c r="B679" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="680">
@@ -15051,7 +15051,7 @@
         <v>46336</v>
       </c>
       <c r="B680" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="681">
@@ -15059,7 +15059,7 @@
         <v>46337</v>
       </c>
       <c r="B681" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="682">
@@ -15067,7 +15067,7 @@
         <v>46338</v>
       </c>
       <c r="B682" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="683">
@@ -15075,7 +15075,7 @@
         <v>46339</v>
       </c>
       <c r="B683" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="684">
@@ -15083,7 +15083,7 @@
         <v>46340</v>
       </c>
       <c r="B684" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="685">
@@ -15091,7 +15091,7 @@
         <v>46341</v>
       </c>
       <c r="B685" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="686">
@@ -15099,7 +15099,7 @@
         <v>46342</v>
       </c>
       <c r="B686" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="687">
@@ -15107,7 +15107,7 @@
         <v>46343</v>
       </c>
       <c r="B687" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="688">
@@ -15115,7 +15115,7 @@
         <v>46344</v>
       </c>
       <c r="B688" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="689">
@@ -15123,7 +15123,7 @@
         <v>46345</v>
       </c>
       <c r="B689" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="690">
@@ -15131,7 +15131,7 @@
         <v>46346</v>
       </c>
       <c r="B690" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="691">
@@ -15139,7 +15139,7 @@
         <v>46347</v>
       </c>
       <c r="B691" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="692">
@@ -15147,7 +15147,7 @@
         <v>46348</v>
       </c>
       <c r="B692" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="693">
@@ -15155,7 +15155,7 @@
         <v>46349</v>
       </c>
       <c r="B693" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="694">
@@ -15163,7 +15163,7 @@
         <v>46350</v>
       </c>
       <c r="B694" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="695">
@@ -15171,7 +15171,7 @@
         <v>46351</v>
       </c>
       <c r="B695" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="696">
@@ -15179,7 +15179,7 @@
         <v>46352</v>
       </c>
       <c r="B696" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="697">
@@ -15187,7 +15187,7 @@
         <v>46353</v>
       </c>
       <c r="B697" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="698">
@@ -15195,7 +15195,7 @@
         <v>46354</v>
       </c>
       <c r="B698" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="699">
@@ -15203,7 +15203,7 @@
         <v>46355</v>
       </c>
       <c r="B699" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="700">
@@ -15211,7 +15211,7 @@
         <v>46356</v>
       </c>
       <c r="B700" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="701">
@@ -15219,7 +15219,7 @@
         <v>46357</v>
       </c>
       <c r="B701" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="702">
@@ -15227,7 +15227,7 @@
         <v>46358</v>
       </c>
       <c r="B702" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="703">
@@ -15235,7 +15235,7 @@
         <v>46359</v>
       </c>
       <c r="B703" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="704">
@@ -15243,7 +15243,7 @@
         <v>46360</v>
       </c>
       <c r="B704" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="705">
@@ -15251,7 +15251,7 @@
         <v>46361</v>
       </c>
       <c r="B705" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="706">
@@ -15259,7 +15259,7 @@
         <v>46362</v>
       </c>
       <c r="B706" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="707">
@@ -15267,7 +15267,7 @@
         <v>46363</v>
       </c>
       <c r="B707" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="708">
@@ -15275,7 +15275,7 @@
         <v>46364</v>
       </c>
       <c r="B708" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="709">
@@ -15283,7 +15283,7 @@
         <v>46365</v>
       </c>
       <c r="B709" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="710">
@@ -15291,7 +15291,7 @@
         <v>46366</v>
       </c>
       <c r="B710" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="711">
@@ -15299,7 +15299,7 @@
         <v>46367</v>
       </c>
       <c r="B711" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="712">
@@ -15307,7 +15307,7 @@
         <v>46368</v>
       </c>
       <c r="B712" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="713">
@@ -15315,7 +15315,7 @@
         <v>46369</v>
       </c>
       <c r="B713" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="714">
@@ -15323,7 +15323,7 @@
         <v>46370</v>
       </c>
       <c r="B714" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="715">
@@ -15331,7 +15331,7 @@
         <v>46371</v>
       </c>
       <c r="B715" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="716">
@@ -15339,7 +15339,7 @@
         <v>46372</v>
       </c>
       <c r="B716" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="717">
@@ -15347,7 +15347,7 @@
         <v>46373</v>
       </c>
       <c r="B717" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="718">
@@ -15355,7 +15355,7 @@
         <v>46374</v>
       </c>
       <c r="B718" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="719">
@@ -15363,7 +15363,7 @@
         <v>46375</v>
       </c>
       <c r="B719" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="720">
@@ -15371,7 +15371,7 @@
         <v>46376</v>
       </c>
       <c r="B720" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="721">
@@ -15379,7 +15379,7 @@
         <v>46377</v>
       </c>
       <c r="B721" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="722">
@@ -15387,7 +15387,7 @@
         <v>46378</v>
       </c>
       <c r="B722" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="723">
@@ -15395,7 +15395,7 @@
         <v>46379</v>
       </c>
       <c r="B723" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="724">
@@ -15403,7 +15403,7 @@
         <v>46380</v>
       </c>
       <c r="B724" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="725">
@@ -15411,7 +15411,7 @@
         <v>46381</v>
       </c>
       <c r="B725" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="726">
@@ -15419,7 +15419,7 @@
         <v>46382</v>
       </c>
       <c r="B726" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="727">
@@ -15427,7 +15427,7 @@
         <v>46383</v>
       </c>
       <c r="B727" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="728">
@@ -15435,7 +15435,7 @@
         <v>46384</v>
       </c>
       <c r="B728" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="729">
@@ -15443,7 +15443,7 @@
         <v>46385</v>
       </c>
       <c r="B729" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="730">
@@ -15451,7 +15451,7 @@
         <v>46386</v>
       </c>
       <c r="B730" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="731">
@@ -15459,7 +15459,7 @@
         <v>46387</v>
       </c>
       <c r="B731" t="n">
-        <v>48.76</v>
+        <v>51.26</v>
       </c>
     </row>
     <row r="732">
@@ -15467,7 +15467,7 @@
         <v>46388</v>
       </c>
       <c r="B732" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="733">
@@ -15475,7 +15475,7 @@
         <v>46389</v>
       </c>
       <c r="B733" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="734">
@@ -15483,7 +15483,7 @@
         <v>46390</v>
       </c>
       <c r="B734" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="735">
@@ -15491,7 +15491,7 @@
         <v>46391</v>
       </c>
       <c r="B735" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="736">
@@ -15499,7 +15499,7 @@
         <v>46392</v>
       </c>
       <c r="B736" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="737">
@@ -15507,7 +15507,7 @@
         <v>46393</v>
       </c>
       <c r="B737" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="738">
@@ -15515,7 +15515,7 @@
         <v>46394</v>
       </c>
       <c r="B738" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="739">
@@ -15523,7 +15523,7 @@
         <v>46395</v>
       </c>
       <c r="B739" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="740">
@@ -15531,7 +15531,7 @@
         <v>46396</v>
       </c>
       <c r="B740" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="741">
@@ -15539,7 +15539,7 @@
         <v>46397</v>
       </c>
       <c r="B741" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="742">
@@ -15547,7 +15547,7 @@
         <v>46398</v>
       </c>
       <c r="B742" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="743">
@@ -15555,7 +15555,7 @@
         <v>46399</v>
       </c>
       <c r="B743" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="744">
@@ -15563,7 +15563,7 @@
         <v>46400</v>
       </c>
       <c r="B744" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="745">
@@ -15571,7 +15571,7 @@
         <v>46401</v>
       </c>
       <c r="B745" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="746">
@@ -15579,7 +15579,7 @@
         <v>46402</v>
       </c>
       <c r="B746" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="747">
@@ -15587,7 +15587,7 @@
         <v>46403</v>
       </c>
       <c r="B747" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="748">
@@ -15595,7 +15595,7 @@
         <v>46404</v>
       </c>
       <c r="B748" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="749">
@@ -15603,7 +15603,7 @@
         <v>46405</v>
       </c>
       <c r="B749" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="750">
@@ -15611,7 +15611,7 @@
         <v>46406</v>
       </c>
       <c r="B750" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="751">
@@ -15619,7 +15619,7 @@
         <v>46407</v>
       </c>
       <c r="B751" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="752">
@@ -15627,7 +15627,7 @@
         <v>46408</v>
       </c>
       <c r="B752" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="753">
@@ -15635,7 +15635,7 @@
         <v>46409</v>
       </c>
       <c r="B753" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="754">
@@ -15643,7 +15643,7 @@
         <v>46410</v>
       </c>
       <c r="B754" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="755">
@@ -15651,7 +15651,7 @@
         <v>46411</v>
       </c>
       <c r="B755" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="756">
@@ -15659,7 +15659,7 @@
         <v>46412</v>
       </c>
       <c r="B756" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="757">
@@ -15667,7 +15667,7 @@
         <v>46413</v>
       </c>
       <c r="B757" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="758">
@@ -15675,7 +15675,7 @@
         <v>46414</v>
       </c>
       <c r="B758" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="759">
@@ -15683,7 +15683,7 @@
         <v>46415</v>
       </c>
       <c r="B759" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="760">
@@ -15691,7 +15691,7 @@
         <v>46416</v>
       </c>
       <c r="B760" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="761">
@@ -15699,7 +15699,7 @@
         <v>46417</v>
       </c>
       <c r="B761" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="762">
@@ -15707,7 +15707,7 @@
         <v>46418</v>
       </c>
       <c r="B762" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="763">
@@ -15715,7 +15715,7 @@
         <v>46419</v>
       </c>
       <c r="B763" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="764">
@@ -15723,7 +15723,7 @@
         <v>46420</v>
       </c>
       <c r="B764" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="765">
@@ -15731,7 +15731,7 @@
         <v>46421</v>
       </c>
       <c r="B765" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="766">
@@ -15739,7 +15739,7 @@
         <v>46422</v>
       </c>
       <c r="B766" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="767">
@@ -15747,7 +15747,7 @@
         <v>46423</v>
       </c>
       <c r="B767" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="768">
@@ -15755,7 +15755,7 @@
         <v>46424</v>
       </c>
       <c r="B768" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="769">
@@ -15763,7 +15763,7 @@
         <v>46425</v>
       </c>
       <c r="B769" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="770">
@@ -15771,7 +15771,7 @@
         <v>46426</v>
       </c>
       <c r="B770" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="771">
@@ -15779,7 +15779,7 @@
         <v>46427</v>
       </c>
       <c r="B771" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="772">
@@ -15787,7 +15787,7 @@
         <v>46428</v>
       </c>
       <c r="B772" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="773">
@@ -15795,7 +15795,7 @@
         <v>46429</v>
       </c>
       <c r="B773" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="774">
@@ -15803,7 +15803,7 @@
         <v>46430</v>
       </c>
       <c r="B774" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="775">
@@ -15811,7 +15811,7 @@
         <v>46431</v>
       </c>
       <c r="B775" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="776">
@@ -15819,7 +15819,7 @@
         <v>46432</v>
       </c>
       <c r="B776" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="777">
@@ -15827,7 +15827,7 @@
         <v>46433</v>
       </c>
       <c r="B777" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="778">
@@ -15835,7 +15835,7 @@
         <v>46434</v>
       </c>
       <c r="B778" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="779">
@@ -15843,7 +15843,7 @@
         <v>46435</v>
       </c>
       <c r="B779" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="780">
@@ -15851,7 +15851,7 @@
         <v>46436</v>
       </c>
       <c r="B780" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="781">
@@ -15859,7 +15859,7 @@
         <v>46437</v>
       </c>
       <c r="B781" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="782">
@@ -15867,7 +15867,7 @@
         <v>46438</v>
       </c>
       <c r="B782" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="783">
@@ -15875,7 +15875,7 @@
         <v>46439</v>
       </c>
       <c r="B783" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="784">
@@ -15883,7 +15883,7 @@
         <v>46440</v>
       </c>
       <c r="B784" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="785">
@@ -15891,7 +15891,7 @@
         <v>46441</v>
       </c>
       <c r="B785" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="786">
@@ -15899,7 +15899,7 @@
         <v>46442</v>
       </c>
       <c r="B786" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="787">
@@ -15907,7 +15907,7 @@
         <v>46443</v>
       </c>
       <c r="B787" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="788">
@@ -15915,7 +15915,7 @@
         <v>46444</v>
       </c>
       <c r="B788" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="789">
@@ -15923,7 +15923,7 @@
         <v>46445</v>
       </c>
       <c r="B789" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="790">
@@ -15931,7 +15931,7 @@
         <v>46446</v>
       </c>
       <c r="B790" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="791">
@@ -15939,7 +15939,7 @@
         <v>46447</v>
       </c>
       <c r="B791" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="792">
@@ -15947,7 +15947,7 @@
         <v>46448</v>
       </c>
       <c r="B792" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="793">
@@ -15955,7 +15955,7 @@
         <v>46449</v>
       </c>
       <c r="B793" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="794">
@@ -15963,7 +15963,7 @@
         <v>46450</v>
       </c>
       <c r="B794" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="795">
@@ -15971,7 +15971,7 @@
         <v>46451</v>
       </c>
       <c r="B795" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="796">
@@ -15979,7 +15979,7 @@
         <v>46452</v>
       </c>
       <c r="B796" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="797">
@@ -15987,7 +15987,7 @@
         <v>46453</v>
       </c>
       <c r="B797" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="798">
@@ -15995,7 +15995,7 @@
         <v>46454</v>
       </c>
       <c r="B798" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="799">
@@ -16003,7 +16003,7 @@
         <v>46455</v>
       </c>
       <c r="B799" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="800">
@@ -16011,7 +16011,7 @@
         <v>46456</v>
       </c>
       <c r="B800" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="801">
@@ -16019,7 +16019,7 @@
         <v>46457</v>
       </c>
       <c r="B801" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="802">
@@ -16027,7 +16027,7 @@
         <v>46458</v>
       </c>
       <c r="B802" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="803">
@@ -16035,7 +16035,7 @@
         <v>46459</v>
       </c>
       <c r="B803" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="804">
@@ -16043,7 +16043,7 @@
         <v>46460</v>
       </c>
       <c r="B804" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="805">
@@ -16051,7 +16051,7 @@
         <v>46461</v>
       </c>
       <c r="B805" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="806">
@@ -16059,7 +16059,7 @@
         <v>46462</v>
       </c>
       <c r="B806" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="807">
@@ -16067,7 +16067,7 @@
         <v>46463</v>
       </c>
       <c r="B807" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="808">
@@ -16075,7 +16075,7 @@
         <v>46464</v>
       </c>
       <c r="B808" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="809">
@@ -16083,7 +16083,7 @@
         <v>46465</v>
       </c>
       <c r="B809" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="810">
@@ -16091,7 +16091,7 @@
         <v>46466</v>
       </c>
       <c r="B810" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="811">
@@ -16099,7 +16099,7 @@
         <v>46467</v>
       </c>
       <c r="B811" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="812">
@@ -16107,7 +16107,7 @@
         <v>46468</v>
       </c>
       <c r="B812" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="813">
@@ -16115,7 +16115,7 @@
         <v>46469</v>
       </c>
       <c r="B813" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="814">
@@ -16123,7 +16123,7 @@
         <v>46470</v>
       </c>
       <c r="B814" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="815">
@@ -16131,7 +16131,7 @@
         <v>46471</v>
       </c>
       <c r="B815" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="816">
@@ -16139,7 +16139,7 @@
         <v>46472</v>
       </c>
       <c r="B816" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="817">
@@ -16147,7 +16147,7 @@
         <v>46473</v>
       </c>
       <c r="B817" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="818">
@@ -16155,7 +16155,7 @@
         <v>46474</v>
       </c>
       <c r="B818" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="819">
@@ -16163,7 +16163,7 @@
         <v>46475</v>
       </c>
       <c r="B819" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="820">
@@ -16171,7 +16171,7 @@
         <v>46476</v>
       </c>
       <c r="B820" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="821">
@@ -16179,7 +16179,7 @@
         <v>46477</v>
       </c>
       <c r="B821" t="n">
-        <v>47.13</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="822">
@@ -16187,7 +16187,7 @@
         <v>46478</v>
       </c>
       <c r="B822" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="823">
@@ -16195,7 +16195,7 @@
         <v>46479</v>
       </c>
       <c r="B823" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="824">
@@ -16203,7 +16203,7 @@
         <v>46480</v>
       </c>
       <c r="B824" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="825">
@@ -16211,7 +16211,7 @@
         <v>46481</v>
       </c>
       <c r="B825" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="826">
@@ -16219,7 +16219,7 @@
         <v>46482</v>
       </c>
       <c r="B826" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="827">
@@ -16227,7 +16227,7 @@
         <v>46483</v>
       </c>
       <c r="B827" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="828">
@@ -16235,7 +16235,7 @@
         <v>46484</v>
       </c>
       <c r="B828" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="829">
@@ -16243,7 +16243,7 @@
         <v>46485</v>
       </c>
       <c r="B829" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="830">
@@ -16251,7 +16251,7 @@
         <v>46486</v>
       </c>
       <c r="B830" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="831">
@@ -16259,7 +16259,7 @@
         <v>46487</v>
       </c>
       <c r="B831" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="832">
@@ -16267,7 +16267,7 @@
         <v>46488</v>
       </c>
       <c r="B832" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="833">
@@ -16275,7 +16275,7 @@
         <v>46489</v>
       </c>
       <c r="B833" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="834">
@@ -16283,7 +16283,7 @@
         <v>46490</v>
       </c>
       <c r="B834" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="835">
@@ -16291,7 +16291,7 @@
         <v>46491</v>
       </c>
       <c r="B835" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="836">
@@ -16299,7 +16299,7 @@
         <v>46492</v>
       </c>
       <c r="B836" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="837">
@@ -16307,7 +16307,7 @@
         <v>46493</v>
       </c>
       <c r="B837" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="838">
@@ -16315,7 +16315,7 @@
         <v>46494</v>
       </c>
       <c r="B838" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="839">
@@ -16323,7 +16323,7 @@
         <v>46495</v>
       </c>
       <c r="B839" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="840">
@@ -16331,7 +16331,7 @@
         <v>46496</v>
       </c>
       <c r="B840" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="841">
@@ -16339,7 +16339,7 @@
         <v>46497</v>
       </c>
       <c r="B841" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="842">
@@ -16347,7 +16347,7 @@
         <v>46498</v>
       </c>
       <c r="B842" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="843">
@@ -16355,7 +16355,7 @@
         <v>46499</v>
       </c>
       <c r="B843" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="844">
@@ -16363,7 +16363,7 @@
         <v>46500</v>
       </c>
       <c r="B844" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="845">
@@ -16371,7 +16371,7 @@
         <v>46501</v>
       </c>
       <c r="B845" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="846">
@@ -16379,7 +16379,7 @@
         <v>46502</v>
       </c>
       <c r="B846" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="847">
@@ -16387,7 +16387,7 @@
         <v>46503</v>
       </c>
       <c r="B847" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="848">
@@ -16395,7 +16395,7 @@
         <v>46504</v>
       </c>
       <c r="B848" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="849">
@@ -16403,7 +16403,7 @@
         <v>46505</v>
       </c>
       <c r="B849" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="850">
@@ -16411,7 +16411,7 @@
         <v>46506</v>
       </c>
       <c r="B850" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="851">
@@ -16419,7 +16419,7 @@
         <v>46507</v>
       </c>
       <c r="B851" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="852">
@@ -16427,7 +16427,7 @@
         <v>46508</v>
       </c>
       <c r="B852" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="853">
@@ -16435,7 +16435,7 @@
         <v>46509</v>
       </c>
       <c r="B853" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="854">
@@ -16443,7 +16443,7 @@
         <v>46510</v>
       </c>
       <c r="B854" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="855">
@@ -16451,7 +16451,7 @@
         <v>46511</v>
       </c>
       <c r="B855" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="856">
@@ -16459,7 +16459,7 @@
         <v>46512</v>
       </c>
       <c r="B856" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="857">
@@ -16467,7 +16467,7 @@
         <v>46513</v>
       </c>
       <c r="B857" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="858">
@@ -16475,7 +16475,7 @@
         <v>46514</v>
       </c>
       <c r="B858" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="859">
@@ -16483,7 +16483,7 @@
         <v>46515</v>
       </c>
       <c r="B859" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="860">
@@ -16491,7 +16491,7 @@
         <v>46516</v>
       </c>
       <c r="B860" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="861">
@@ -16499,7 +16499,7 @@
         <v>46517</v>
       </c>
       <c r="B861" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="862">
@@ -16507,7 +16507,7 @@
         <v>46518</v>
       </c>
       <c r="B862" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="863">
@@ -16515,7 +16515,7 @@
         <v>46519</v>
       </c>
       <c r="B863" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="864">
@@ -16523,7 +16523,7 @@
         <v>46520</v>
       </c>
       <c r="B864" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="865">
@@ -16531,7 +16531,7 @@
         <v>46521</v>
       </c>
       <c r="B865" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="866">
@@ -16539,7 +16539,7 @@
         <v>46522</v>
       </c>
       <c r="B866" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="867">
@@ -16547,7 +16547,7 @@
         <v>46523</v>
       </c>
       <c r="B867" t="n">
-        <v>35.14</v>
+        <v>35.15</v>
       </c>
     </row>
  